--- a/ChilwaBasin_DataAnalysis_032024/Dataset/ChilwaBasin_LakeDepth_20250929.xlsx
+++ b/ChilwaBasin_DataAnalysis_032024/Dataset/ChilwaBasin_LakeDepth_20250929.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ali\OneDrive\Desktop\Chilwa Basin Update files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ali\Documents\GitHub\ChilwaBasin\ChilwaBasin_DataAnalysis_032024\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266C983F-9A1D-4265-A2B0-B79FDB96A9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326E53F5-104C-49EA-9A3C-B2A0D4B53563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{E52436F2-D984-4EE3-B8A0-F9D4A91B50A0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" firstSheet="5" activeTab="9" xr2:uid="{E52436F2-D984-4EE3-B8A0-F9D4A91B50A0}"/>
   </bookViews>
   <sheets>
     <sheet name="DepthCatchCyclone" sheetId="10" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="MeanAnnualDepthMacuiane_2011" sheetId="4" r:id="rId7"/>
     <sheet name="Depth_Kalk_1979" sheetId="3" r:id="rId8"/>
     <sheet name="TotalCatch_Njaya_2011" sheetId="6" r:id="rId9"/>
+    <sheet name="Depth_Kalk_1979 (Verify)" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChilwaBasinMonthlyDataset-Old'!$A$1:$B$733</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3708" uniqueCount="1065">
   <si>
     <t>Date</t>
   </si>
@@ -3370,7 +3371,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3413,6 +3414,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -7892,7 +7894,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Depth_Kalk_1979!$C$2:$C$325</c:f>
+              <c:f>'Depth_Kalk_1979 (Verify)'!$C$2:$C$325</c:f>
               <c:strCache>
                 <c:ptCount val="324"/>
                 <c:pt idx="0">
@@ -8872,7 +8874,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Depth_Kalk_1979!$D$2:$D$325</c:f>
+              <c:f>'Depth_Kalk_1979 (Verify)'!$D$2:$D$325</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="324"/>
@@ -9854,7 +9856,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B40E-4EB5-8A14-B9E621A422E9}"/>
+              <c16:uniqueId val="{00000000-28F3-4B73-B454-E44BE508CEE6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10096,7 +10098,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Depth_Kalk_1979!$A$2:$A$139</c:f>
+              <c:f>'Depth_Kalk_1979 (Verify)'!$A$2:$A$139</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="138"/>
@@ -10519,7 +10521,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Depth_Kalk_1979!$B$2:$B$139</c:f>
+              <c:f>'Depth_Kalk_1979 (Verify)'!$B$2:$B$139</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="138"/>
@@ -10943,7 +10945,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B40E-4EB5-8A14-B9E621A422E9}"/>
+              <c16:uniqueId val="{00000000-C65B-4C9F-8B2D-6480D088F881}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12844,10 +12846,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FBC39FA-EF70-41D7-BCC1-48DA1657F5CD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34E791E-4871-4ACA-99AD-E3A252BE8F92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12882,10 +12884,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB9C6B0E-21B8-3DD2-F7AD-28728023A050}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5469AB9-E559-4701-A337-89516040F668}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -27185,9 +27187,6 @@
       <c r="B698" t="s">
         <v>1063</v>
       </c>
-      <c r="D698">
-        <v>0</v>
-      </c>
       <c r="E698" t="s">
         <v>1063</v>
       </c>
@@ -27205,9 +27204,6 @@
       <c r="B699" t="s">
         <v>1063</v>
       </c>
-      <c r="D699">
-        <v>0</v>
-      </c>
       <c r="E699" t="s">
         <v>1063</v>
       </c>
@@ -27225,9 +27221,6 @@
       <c r="B700" t="s">
         <v>1063</v>
       </c>
-      <c r="D700">
-        <v>0</v>
-      </c>
       <c r="E700" t="s">
         <v>1063</v>
       </c>
@@ -27245,9 +27238,6 @@
       <c r="B701" t="s">
         <v>1063</v>
       </c>
-      <c r="D701">
-        <v>0</v>
-      </c>
       <c r="E701" t="s">
         <v>1063</v>
       </c>
@@ -27265,9 +27255,6 @@
       <c r="B702" t="s">
         <v>1063</v>
       </c>
-      <c r="D702">
-        <v>0</v>
-      </c>
       <c r="E702" t="s">
         <v>1063</v>
       </c>
@@ -27285,9 +27272,6 @@
       <c r="B703" t="s">
         <v>1063</v>
       </c>
-      <c r="D703">
-        <v>0</v>
-      </c>
       <c r="E703" t="s">
         <v>1063</v>
       </c>
@@ -27305,9 +27289,6 @@
       <c r="B704" t="s">
         <v>1063</v>
       </c>
-      <c r="D704">
-        <v>0</v>
-      </c>
       <c r="E704" t="s">
         <v>1063</v>
       </c>
@@ -27325,9 +27306,6 @@
       <c r="B705" t="s">
         <v>1063</v>
       </c>
-      <c r="D705">
-        <v>0</v>
-      </c>
       <c r="E705" t="s">
         <v>1063</v>
       </c>
@@ -27345,9 +27323,6 @@
       <c r="B706" t="s">
         <v>1063</v>
       </c>
-      <c r="D706">
-        <v>0</v>
-      </c>
       <c r="E706" t="s">
         <v>1063</v>
       </c>
@@ -27365,9 +27340,6 @@
       <c r="B707" t="s">
         <v>1063</v>
       </c>
-      <c r="D707">
-        <v>0</v>
-      </c>
       <c r="E707" t="s">
         <v>1063</v>
       </c>
@@ -27385,9 +27357,6 @@
       <c r="B708" t="s">
         <v>1063</v>
       </c>
-      <c r="D708">
-        <v>0</v>
-      </c>
       <c r="E708" t="s">
         <v>1063</v>
       </c>
@@ -27405,9 +27374,6 @@
       <c r="B709" t="s">
         <v>1063</v>
       </c>
-      <c r="D709">
-        <v>0</v>
-      </c>
       <c r="E709" t="s">
         <v>1063</v>
       </c>
@@ -27425,9 +27391,6 @@
       <c r="B710" t="s">
         <v>1063</v>
       </c>
-      <c r="D710">
-        <v>0</v>
-      </c>
       <c r="E710" t="s">
         <v>1063</v>
       </c>
@@ -27445,9 +27408,6 @@
       <c r="B711" t="s">
         <v>1063</v>
       </c>
-      <c r="D711">
-        <v>0</v>
-      </c>
       <c r="E711" t="s">
         <v>1063</v>
       </c>
@@ -27465,9 +27425,6 @@
       <c r="B712" t="s">
         <v>1063</v>
       </c>
-      <c r="D712">
-        <v>0</v>
-      </c>
       <c r="E712" t="s">
         <v>1063</v>
       </c>
@@ -27485,9 +27442,6 @@
       <c r="B713" t="s">
         <v>1063</v>
       </c>
-      <c r="D713">
-        <v>0</v>
-      </c>
       <c r="E713" t="s">
         <v>1063</v>
       </c>
@@ -27505,9 +27459,6 @@
       <c r="B714" t="s">
         <v>1063</v>
       </c>
-      <c r="D714">
-        <v>0</v>
-      </c>
       <c r="E714" t="s">
         <v>1063</v>
       </c>
@@ -27525,9 +27476,6 @@
       <c r="B715" t="s">
         <v>1063</v>
       </c>
-      <c r="D715">
-        <v>0</v>
-      </c>
       <c r="E715" t="s">
         <v>1063</v>
       </c>
@@ -27545,9 +27493,6 @@
       <c r="B716" t="s">
         <v>1063</v>
       </c>
-      <c r="D716">
-        <v>0</v>
-      </c>
       <c r="E716" t="s">
         <v>1063</v>
       </c>
@@ -27565,9 +27510,6 @@
       <c r="B717" t="s">
         <v>1063</v>
       </c>
-      <c r="D717">
-        <v>0</v>
-      </c>
       <c r="E717" t="s">
         <v>1063</v>
       </c>
@@ -27585,9 +27527,6 @@
       <c r="B718" t="s">
         <v>1063</v>
       </c>
-      <c r="D718">
-        <v>0</v>
-      </c>
       <c r="E718" t="s">
         <v>1063</v>
       </c>
@@ -27605,9 +27544,6 @@
       <c r="B719" t="s">
         <v>1063</v>
       </c>
-      <c r="D719">
-        <v>0</v>
-      </c>
       <c r="E719" t="s">
         <v>1063</v>
       </c>
@@ -27625,9 +27561,6 @@
       <c r="B720" t="s">
         <v>1063</v>
       </c>
-      <c r="D720">
-        <v>0</v>
-      </c>
       <c r="E720" t="s">
         <v>1063</v>
       </c>
@@ -27645,9 +27578,6 @@
       <c r="B721" t="s">
         <v>1063</v>
       </c>
-      <c r="D721">
-        <v>0</v>
-      </c>
       <c r="E721" t="s">
         <v>1063</v>
       </c>
@@ -27665,9 +27595,6 @@
       <c r="B722" t="s">
         <v>1063</v>
       </c>
-      <c r="D722">
-        <v>0</v>
-      </c>
       <c r="E722" t="s">
         <v>1063</v>
       </c>
@@ -27685,9 +27612,6 @@
       <c r="B723" t="s">
         <v>1063</v>
       </c>
-      <c r="D723">
-        <v>0</v>
-      </c>
       <c r="E723" t="s">
         <v>1063</v>
       </c>
@@ -27705,9 +27629,6 @@
       <c r="B724" t="s">
         <v>1063</v>
       </c>
-      <c r="D724">
-        <v>0</v>
-      </c>
       <c r="E724" t="s">
         <v>1063</v>
       </c>
@@ -27725,9 +27646,6 @@
       <c r="B725" t="s">
         <v>1063</v>
       </c>
-      <c r="D725">
-        <v>0</v>
-      </c>
       <c r="E725" t="s">
         <v>1063</v>
       </c>
@@ -27745,9 +27663,6 @@
       <c r="B726" t="s">
         <v>1063</v>
       </c>
-      <c r="D726">
-        <v>0</v>
-      </c>
       <c r="E726" t="s">
         <v>1063</v>
       </c>
@@ -27765,9 +27680,6 @@
       <c r="B727" t="s">
         <v>1063</v>
       </c>
-      <c r="D727">
-        <v>0</v>
-      </c>
       <c r="E727" t="s">
         <v>1063</v>
       </c>
@@ -27785,9 +27697,6 @@
       <c r="B728" t="s">
         <v>1063</v>
       </c>
-      <c r="D728">
-        <v>0</v>
-      </c>
       <c r="E728" t="s">
         <v>1063</v>
       </c>
@@ -27805,9 +27714,6 @@
       <c r="B729" t="s">
         <v>1063</v>
       </c>
-      <c r="D729">
-        <v>0</v>
-      </c>
       <c r="E729" t="s">
         <v>1063</v>
       </c>
@@ -27825,9 +27731,6 @@
       <c r="B730" t="s">
         <v>1063</v>
       </c>
-      <c r="D730">
-        <v>0</v>
-      </c>
       <c r="E730" t="s">
         <v>1063</v>
       </c>
@@ -27845,9 +27748,6 @@
       <c r="B731" t="s">
         <v>1063</v>
       </c>
-      <c r="D731">
-        <v>0</v>
-      </c>
       <c r="E731" t="s">
         <v>1063</v>
       </c>
@@ -27865,9 +27765,6 @@
       <c r="B732" t="s">
         <v>1063</v>
       </c>
-      <c r="D732">
-        <v>0</v>
-      </c>
       <c r="E732" t="s">
         <v>1063</v>
       </c>
@@ -27885,9 +27782,6 @@
       <c r="B733" t="s">
         <v>1063</v>
       </c>
-      <c r="D733">
-        <v>0</v>
-      </c>
       <c r="E733" t="s">
         <v>1063</v>
       </c>
@@ -27905,9 +27799,6 @@
       <c r="B734" t="s">
         <v>1063</v>
       </c>
-      <c r="D734">
-        <v>0</v>
-      </c>
       <c r="E734" t="s">
         <v>1063</v>
       </c>
@@ -27925,9 +27816,6 @@
       <c r="B735" t="s">
         <v>1063</v>
       </c>
-      <c r="D735">
-        <v>0</v>
-      </c>
       <c r="E735" t="s">
         <v>1063</v>
       </c>
@@ -27945,9 +27833,6 @@
       <c r="B736" t="s">
         <v>1063</v>
       </c>
-      <c r="D736">
-        <v>0</v>
-      </c>
       <c r="E736" t="s">
         <v>1063</v>
       </c>
@@ -27965,9 +27850,6 @@
       <c r="B737" t="s">
         <v>1063</v>
       </c>
-      <c r="D737">
-        <v>0</v>
-      </c>
       <c r="E737" t="s">
         <v>1063</v>
       </c>
@@ -27985,9 +27867,6 @@
       <c r="B738" t="s">
         <v>1063</v>
       </c>
-      <c r="D738">
-        <v>0</v>
-      </c>
       <c r="E738" t="s">
         <v>1063</v>
       </c>
@@ -28005,9 +27884,6 @@
       <c r="B739" t="s">
         <v>1063</v>
       </c>
-      <c r="D739">
-        <v>0</v>
-      </c>
       <c r="E739" t="s">
         <v>1063</v>
       </c>
@@ -28025,9 +27901,6 @@
       <c r="B740" t="s">
         <v>1063</v>
       </c>
-      <c r="D740">
-        <v>0</v>
-      </c>
       <c r="E740" t="s">
         <v>1063</v>
       </c>
@@ -28045,9 +27918,6 @@
       <c r="B741" t="s">
         <v>1063</v>
       </c>
-      <c r="D741">
-        <v>0</v>
-      </c>
       <c r="E741" t="s">
         <v>1063</v>
       </c>
@@ -28065,9 +27935,6 @@
       <c r="B742" t="s">
         <v>1063</v>
       </c>
-      <c r="D742">
-        <v>0</v>
-      </c>
       <c r="E742" t="s">
         <v>1063</v>
       </c>
@@ -28085,9 +27952,6 @@
       <c r="B743" t="s">
         <v>1063</v>
       </c>
-      <c r="D743">
-        <v>0</v>
-      </c>
       <c r="E743" t="s">
         <v>1063</v>
       </c>
@@ -28105,9 +27969,6 @@
       <c r="B744" t="s">
         <v>1063</v>
       </c>
-      <c r="D744">
-        <v>0</v>
-      </c>
       <c r="E744" t="s">
         <v>1063</v>
       </c>
@@ -28125,9 +27986,6 @@
       <c r="B745" t="s">
         <v>1063</v>
       </c>
-      <c r="D745">
-        <v>0</v>
-      </c>
       <c r="E745" t="s">
         <v>1063</v>
       </c>
@@ -28148,9 +28006,6 @@
       <c r="C746" t="s">
         <v>50</v>
       </c>
-      <c r="D746">
-        <v>0</v>
-      </c>
       <c r="E746" t="s">
         <v>1063</v>
       </c>
@@ -28168,9 +28023,6 @@
       <c r="B747" t="s">
         <v>1063</v>
       </c>
-      <c r="D747">
-        <v>0</v>
-      </c>
       <c r="E747" t="s">
         <v>1063</v>
       </c>
@@ -28188,9 +28040,6 @@
       <c r="B748" t="s">
         <v>1063</v>
       </c>
-      <c r="D748">
-        <v>0</v>
-      </c>
       <c r="E748" t="s">
         <v>1063</v>
       </c>
@@ -28208,9 +28057,6 @@
       <c r="B749" t="s">
         <v>1063</v>
       </c>
-      <c r="D749">
-        <v>0</v>
-      </c>
       <c r="E749" t="s">
         <v>1063</v>
       </c>
@@ -28228,9 +28074,6 @@
       <c r="B750" t="s">
         <v>1063</v>
       </c>
-      <c r="D750">
-        <v>0</v>
-      </c>
       <c r="E750" t="s">
         <v>1063</v>
       </c>
@@ -28248,9 +28091,6 @@
       <c r="B751" t="s">
         <v>1063</v>
       </c>
-      <c r="D751">
-        <v>0</v>
-      </c>
       <c r="E751" t="s">
         <v>1063</v>
       </c>
@@ -28268,9 +28108,6 @@
       <c r="B752" t="s">
         <v>1063</v>
       </c>
-      <c r="D752">
-        <v>0</v>
-      </c>
       <c r="E752" t="s">
         <v>1063</v>
       </c>
@@ -28288,9 +28125,6 @@
       <c r="B753" t="s">
         <v>1063</v>
       </c>
-      <c r="D753">
-        <v>0</v>
-      </c>
       <c r="E753" t="s">
         <v>1063</v>
       </c>
@@ -28308,9 +28142,6 @@
       <c r="B754" t="s">
         <v>1063</v>
       </c>
-      <c r="D754">
-        <v>0</v>
-      </c>
       <c r="E754" t="s">
         <v>1063</v>
       </c>
@@ -28328,9 +28159,6 @@
       <c r="B755" t="s">
         <v>1063</v>
       </c>
-      <c r="D755">
-        <v>0</v>
-      </c>
       <c r="E755" t="s">
         <v>1063</v>
       </c>
@@ -28348,9 +28176,6 @@
       <c r="B756" t="s">
         <v>1063</v>
       </c>
-      <c r="D756">
-        <v>0</v>
-      </c>
       <c r="E756" t="s">
         <v>1063</v>
       </c>
@@ -28368,9 +28193,6 @@
       <c r="B757" t="s">
         <v>1063</v>
       </c>
-      <c r="D757">
-        <v>0</v>
-      </c>
       <c r="E757" t="s">
         <v>1063</v>
       </c>
@@ -28388,9 +28210,6 @@
       <c r="B758" t="s">
         <v>1063</v>
       </c>
-      <c r="D758">
-        <v>0</v>
-      </c>
       <c r="E758" t="s">
         <v>1063</v>
       </c>
@@ -28408,9 +28227,6 @@
       <c r="B759" t="s">
         <v>1063</v>
       </c>
-      <c r="D759">
-        <v>0</v>
-      </c>
       <c r="E759" t="s">
         <v>1063</v>
       </c>
@@ -28428,9 +28244,6 @@
       <c r="B760" t="s">
         <v>1063</v>
       </c>
-      <c r="D760">
-        <v>0</v>
-      </c>
       <c r="E760" t="s">
         <v>1063</v>
       </c>
@@ -28448,9 +28261,6 @@
       <c r="B761" t="s">
         <v>1063</v>
       </c>
-      <c r="D761">
-        <v>0</v>
-      </c>
       <c r="E761" t="s">
         <v>1063</v>
       </c>
@@ -28468,9 +28278,6 @@
       <c r="B762" t="s">
         <v>1063</v>
       </c>
-      <c r="D762">
-        <v>0</v>
-      </c>
       <c r="E762" t="s">
         <v>1063</v>
       </c>
@@ -28488,9 +28295,6 @@
       <c r="B763" t="s">
         <v>1063</v>
       </c>
-      <c r="D763">
-        <v>0</v>
-      </c>
       <c r="E763" t="s">
         <v>1063</v>
       </c>
@@ -28508,9 +28312,6 @@
       <c r="B764" t="s">
         <v>1063</v>
       </c>
-      <c r="D764">
-        <v>0</v>
-      </c>
       <c r="E764" t="s">
         <v>1063</v>
       </c>
@@ -28528,9 +28329,6 @@
       <c r="B765" t="s">
         <v>1063</v>
       </c>
-      <c r="D765">
-        <v>0</v>
-      </c>
       <c r="E765" t="s">
         <v>1063</v>
       </c>
@@ -28548,9 +28346,6 @@
       <c r="B766" t="s">
         <v>1063</v>
       </c>
-      <c r="D766">
-        <v>0</v>
-      </c>
       <c r="E766" t="s">
         <v>1063</v>
       </c>
@@ -28568,9 +28363,6 @@
       <c r="B767" t="s">
         <v>1063</v>
       </c>
-      <c r="D767">
-        <v>0</v>
-      </c>
       <c r="E767" t="s">
         <v>1063</v>
       </c>
@@ -28588,9 +28380,6 @@
       <c r="B768" t="s">
         <v>1063</v>
       </c>
-      <c r="D768">
-        <v>0</v>
-      </c>
       <c r="E768" t="s">
         <v>1063</v>
       </c>
@@ -28608,9 +28397,6 @@
       <c r="B769" t="s">
         <v>1063</v>
       </c>
-      <c r="D769">
-        <v>0</v>
-      </c>
       <c r="E769" t="s">
         <v>1063</v>
       </c>
@@ -28628,9 +28414,6 @@
       <c r="B770" t="s">
         <v>1063</v>
       </c>
-      <c r="D770">
-        <v>0</v>
-      </c>
       <c r="E770" t="s">
         <v>1063</v>
       </c>
@@ -28648,9 +28431,6 @@
       <c r="B771" t="s">
         <v>1063</v>
       </c>
-      <c r="D771">
-        <v>0</v>
-      </c>
       <c r="E771" t="s">
         <v>1063</v>
       </c>
@@ -28668,9 +28448,6 @@
       <c r="B772" t="s">
         <v>1063</v>
       </c>
-      <c r="D772">
-        <v>0</v>
-      </c>
       <c r="E772" t="s">
         <v>1063</v>
       </c>
@@ -28688,9 +28465,6 @@
       <c r="B773" t="s">
         <v>1063</v>
       </c>
-      <c r="D773">
-        <v>0</v>
-      </c>
       <c r="E773" t="s">
         <v>1063</v>
       </c>
@@ -28708,9 +28482,6 @@
       <c r="B774" t="s">
         <v>1063</v>
       </c>
-      <c r="D774">
-        <v>0</v>
-      </c>
       <c r="E774" t="s">
         <v>1063</v>
       </c>
@@ -28728,9 +28499,6 @@
       <c r="B775" t="s">
         <v>1063</v>
       </c>
-      <c r="D775">
-        <v>0</v>
-      </c>
       <c r="E775" t="s">
         <v>1063</v>
       </c>
@@ -28748,9 +28516,6 @@
       <c r="B776" t="s">
         <v>1063</v>
       </c>
-      <c r="D776">
-        <v>0</v>
-      </c>
       <c r="E776" t="s">
         <v>1063</v>
       </c>
@@ -28768,9 +28533,6 @@
       <c r="B777" t="s">
         <v>1063</v>
       </c>
-      <c r="D777">
-        <v>0</v>
-      </c>
       <c r="E777" t="s">
         <v>1063</v>
       </c>
@@ -28788,9 +28550,6 @@
       <c r="B778" t="s">
         <v>1063</v>
       </c>
-      <c r="D778">
-        <v>0</v>
-      </c>
       <c r="E778" t="s">
         <v>1063</v>
       </c>
@@ -28808,9 +28567,6 @@
       <c r="B779" t="s">
         <v>1063</v>
       </c>
-      <c r="D779">
-        <v>0</v>
-      </c>
       <c r="E779" t="s">
         <v>1063</v>
       </c>
@@ -28828,9 +28584,6 @@
       <c r="B780" t="s">
         <v>1063</v>
       </c>
-      <c r="D780">
-        <v>0</v>
-      </c>
       <c r="E780" t="s">
         <v>1063</v>
       </c>
@@ -28848,9 +28601,6 @@
       <c r="B781" t="s">
         <v>1063</v>
       </c>
-      <c r="D781">
-        <v>0</v>
-      </c>
       <c r="E781" t="s">
         <v>1063</v>
       </c>
@@ -28868,9 +28618,6 @@
       <c r="B782" t="s">
         <v>1063</v>
       </c>
-      <c r="D782">
-        <v>0</v>
-      </c>
       <c r="E782" t="s">
         <v>1063</v>
       </c>
@@ -28888,9 +28635,6 @@
       <c r="B783" t="s">
         <v>1063</v>
       </c>
-      <c r="D783">
-        <v>0</v>
-      </c>
       <c r="E783" t="s">
         <v>1063</v>
       </c>
@@ -28908,9 +28652,6 @@
       <c r="B784" t="s">
         <v>1063</v>
       </c>
-      <c r="D784">
-        <v>0</v>
-      </c>
       <c r="E784" t="s">
         <v>1063</v>
       </c>
@@ -28928,9 +28669,6 @@
       <c r="B785" t="s">
         <v>1063</v>
       </c>
-      <c r="D785">
-        <v>0</v>
-      </c>
       <c r="E785" t="s">
         <v>1063</v>
       </c>
@@ -28948,9 +28686,6 @@
       <c r="B786" t="s">
         <v>1063</v>
       </c>
-      <c r="D786">
-        <v>0</v>
-      </c>
       <c r="E786" t="s">
         <v>1063</v>
       </c>
@@ -28968,9 +28703,6 @@
       <c r="B787" t="s">
         <v>1063</v>
       </c>
-      <c r="D787">
-        <v>0</v>
-      </c>
       <c r="E787" t="s">
         <v>1063</v>
       </c>
@@ -28988,9 +28720,6 @@
       <c r="B788" t="s">
         <v>1063</v>
       </c>
-      <c r="D788">
-        <v>0</v>
-      </c>
       <c r="E788" t="s">
         <v>1063</v>
       </c>
@@ -29008,9 +28737,6 @@
       <c r="B789" t="s">
         <v>1063</v>
       </c>
-      <c r="D789">
-        <v>0</v>
-      </c>
       <c r="E789" t="s">
         <v>1063</v>
       </c>
@@ -29028,9 +28754,6 @@
       <c r="B790" t="s">
         <v>1063</v>
       </c>
-      <c r="D790">
-        <v>0</v>
-      </c>
       <c r="E790" t="s">
         <v>1063</v>
       </c>
@@ -29048,9 +28771,6 @@
       <c r="B791" t="s">
         <v>1063</v>
       </c>
-      <c r="D791">
-        <v>0</v>
-      </c>
       <c r="E791" t="s">
         <v>1063</v>
       </c>
@@ -29068,9 +28788,6 @@
       <c r="B792" t="s">
         <v>1063</v>
       </c>
-      <c r="D792">
-        <v>0</v>
-      </c>
       <c r="E792" t="s">
         <v>1063</v>
       </c>
@@ -29088,9 +28805,6 @@
       <c r="B793" t="s">
         <v>1063</v>
       </c>
-      <c r="D793">
-        <v>0</v>
-      </c>
       <c r="E793" t="s">
         <v>1063</v>
       </c>
@@ -29108,9 +28822,6 @@
       <c r="B794" t="s">
         <v>1063</v>
       </c>
-      <c r="D794">
-        <v>0</v>
-      </c>
       <c r="E794" t="s">
         <v>1063</v>
       </c>
@@ -29128,9 +28839,6 @@
       <c r="B795" t="s">
         <v>1063</v>
       </c>
-      <c r="D795">
-        <v>0</v>
-      </c>
       <c r="E795" t="s">
         <v>1063</v>
       </c>
@@ -29148,9 +28856,6 @@
       <c r="B796" t="s">
         <v>1063</v>
       </c>
-      <c r="D796">
-        <v>0</v>
-      </c>
       <c r="E796" t="s">
         <v>1063</v>
       </c>
@@ -29168,9 +28873,6 @@
       <c r="B797" t="s">
         <v>1063</v>
       </c>
-      <c r="D797">
-        <v>0</v>
-      </c>
       <c r="E797" t="s">
         <v>1063</v>
       </c>
@@ -29188,9 +28890,6 @@
       <c r="B798" t="s">
         <v>1063</v>
       </c>
-      <c r="D798">
-        <v>0</v>
-      </c>
       <c r="E798" t="s">
         <v>1063</v>
       </c>
@@ -29208,9 +28907,6 @@
       <c r="B799" t="s">
         <v>1063</v>
       </c>
-      <c r="D799">
-        <v>0</v>
-      </c>
       <c r="E799" t="s">
         <v>1063</v>
       </c>
@@ -29228,9 +28924,6 @@
       <c r="B800" t="s">
         <v>1063</v>
       </c>
-      <c r="D800">
-        <v>0</v>
-      </c>
       <c r="E800" t="s">
         <v>1063</v>
       </c>
@@ -29248,9 +28941,6 @@
       <c r="B801" t="s">
         <v>1063</v>
       </c>
-      <c r="D801">
-        <v>0</v>
-      </c>
       <c r="E801" t="s">
         <v>1063</v>
       </c>
@@ -29268,9 +28958,6 @@
       <c r="B802" t="s">
         <v>1063</v>
       </c>
-      <c r="D802">
-        <v>0</v>
-      </c>
       <c r="E802" t="s">
         <v>1063</v>
       </c>
@@ -29288,9 +28975,6 @@
       <c r="B803" t="s">
         <v>1063</v>
       </c>
-      <c r="D803">
-        <v>0</v>
-      </c>
       <c r="E803" t="s">
         <v>1063</v>
       </c>
@@ -29308,9 +28992,6 @@
       <c r="B804" t="s">
         <v>1063</v>
       </c>
-      <c r="D804">
-        <v>0</v>
-      </c>
       <c r="E804" t="s">
         <v>1063</v>
       </c>
@@ -29328,9 +29009,6 @@
       <c r="B805" t="s">
         <v>1063</v>
       </c>
-      <c r="D805">
-        <v>0</v>
-      </c>
       <c r="E805" t="s">
         <v>1063</v>
       </c>
@@ -29348,9 +29026,6 @@
       <c r="B806" t="s">
         <v>1063</v>
       </c>
-      <c r="D806">
-        <v>0</v>
-      </c>
       <c r="E806" t="s">
         <v>1063</v>
       </c>
@@ -29371,9 +29046,6 @@
       <c r="C807" t="s">
         <v>57</v>
       </c>
-      <c r="D807">
-        <v>0</v>
-      </c>
       <c r="E807" t="s">
         <v>1063</v>
       </c>
@@ -29391,9 +29063,6 @@
       <c r="B808" t="s">
         <v>1063</v>
       </c>
-      <c r="D808">
-        <v>0</v>
-      </c>
       <c r="E808" t="s">
         <v>1063</v>
       </c>
@@ -29411,9 +29080,6 @@
       <c r="B809" t="s">
         <v>1063</v>
       </c>
-      <c r="D809">
-        <v>0</v>
-      </c>
       <c r="E809" t="s">
         <v>1063</v>
       </c>
@@ -29431,9 +29097,6 @@
       <c r="B810" t="s">
         <v>1063</v>
       </c>
-      <c r="D810">
-        <v>0</v>
-      </c>
       <c r="E810" t="s">
         <v>1063</v>
       </c>
@@ -29451,9 +29114,6 @@
       <c r="B811" t="s">
         <v>1063</v>
       </c>
-      <c r="D811">
-        <v>0</v>
-      </c>
       <c r="E811" t="s">
         <v>1063</v>
       </c>
@@ -29471,9 +29131,6 @@
       <c r="B812" t="s">
         <v>1063</v>
       </c>
-      <c r="D812">
-        <v>0</v>
-      </c>
       <c r="E812" t="s">
         <v>1063</v>
       </c>
@@ -29491,9 +29148,6 @@
       <c r="B813" t="s">
         <v>1063</v>
       </c>
-      <c r="D813">
-        <v>0</v>
-      </c>
       <c r="E813" t="s">
         <v>1063</v>
       </c>
@@ -29511,9 +29165,6 @@
       <c r="B814" t="s">
         <v>1063</v>
       </c>
-      <c r="D814">
-        <v>0</v>
-      </c>
       <c r="E814" t="s">
         <v>1063</v>
       </c>
@@ -29531,9 +29182,6 @@
       <c r="B815" t="s">
         <v>1063</v>
       </c>
-      <c r="D815">
-        <v>0</v>
-      </c>
       <c r="E815" t="s">
         <v>1063</v>
       </c>
@@ -29551,9 +29199,6 @@
       <c r="B816" t="s">
         <v>1063</v>
       </c>
-      <c r="D816">
-        <v>0</v>
-      </c>
       <c r="E816" t="s">
         <v>1063</v>
       </c>
@@ -29571,9 +29216,6 @@
       <c r="B817" t="s">
         <v>1063</v>
       </c>
-      <c r="D817">
-        <v>0</v>
-      </c>
       <c r="E817" t="s">
         <v>1063</v>
       </c>
@@ -29591,9 +29233,6 @@
       <c r="B818" t="s">
         <v>1063</v>
       </c>
-      <c r="D818">
-        <v>0</v>
-      </c>
       <c r="E818" t="s">
         <v>1063</v>
       </c>
@@ -29611,9 +29250,6 @@
       <c r="B819" t="s">
         <v>1063</v>
       </c>
-      <c r="D819">
-        <v>0</v>
-      </c>
       <c r="E819" t="s">
         <v>1063</v>
       </c>
@@ -29631,9 +29267,6 @@
       <c r="B820" t="s">
         <v>1063</v>
       </c>
-      <c r="D820">
-        <v>0</v>
-      </c>
       <c r="E820" t="s">
         <v>1063</v>
       </c>
@@ -29651,9 +29284,6 @@
       <c r="B821" t="s">
         <v>1063</v>
       </c>
-      <c r="D821">
-        <v>0</v>
-      </c>
       <c r="E821" t="s">
         <v>1063</v>
       </c>
@@ -29671,9 +29301,6 @@
       <c r="B822" t="s">
         <v>1063</v>
       </c>
-      <c r="D822">
-        <v>0</v>
-      </c>
       <c r="E822" t="s">
         <v>1063</v>
       </c>
@@ -29691,9 +29318,6 @@
       <c r="B823">
         <v>0.9</v>
       </c>
-      <c r="D823">
-        <v>0</v>
-      </c>
       <c r="E823">
         <v>0.9</v>
       </c>
@@ -29711,9 +29335,6 @@
       <c r="B824">
         <v>1</v>
       </c>
-      <c r="D824">
-        <v>0</v>
-      </c>
       <c r="E824">
         <v>1</v>
       </c>
@@ -29731,9 +29352,6 @@
       <c r="B825">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D825">
-        <v>0</v>
-      </c>
       <c r="E825">
         <v>1.1000000000000001</v>
       </c>
@@ -29751,9 +29369,6 @@
       <c r="B826">
         <v>1.2</v>
       </c>
-      <c r="D826">
-        <v>0</v>
-      </c>
       <c r="E826">
         <v>1.2</v>
       </c>
@@ -29771,9 +29386,6 @@
       <c r="B827">
         <v>1.3</v>
       </c>
-      <c r="D827">
-        <v>0</v>
-      </c>
       <c r="E827">
         <v>1.3</v>
       </c>
@@ -29791,9 +29403,6 @@
       <c r="B828">
         <v>1.4</v>
       </c>
-      <c r="D828">
-        <v>0</v>
-      </c>
       <c r="E828">
         <v>1.4</v>
       </c>
@@ -29811,9 +29420,6 @@
       <c r="B829">
         <v>1.5</v>
       </c>
-      <c r="D829">
-        <v>0</v>
-      </c>
       <c r="E829">
         <v>1.5</v>
       </c>
@@ -29831,9 +29437,6 @@
       <c r="B830">
         <v>1.5</v>
       </c>
-      <c r="D830">
-        <v>0</v>
-      </c>
       <c r="E830">
         <v>1.5</v>
       </c>
@@ -29851,9 +29454,6 @@
       <c r="B831">
         <v>1</v>
       </c>
-      <c r="D831">
-        <v>0</v>
-      </c>
       <c r="E831">
         <v>1</v>
       </c>
@@ -29874,9 +29474,6 @@
       <c r="C832" t="s">
         <v>62</v>
       </c>
-      <c r="D832">
-        <v>0</v>
-      </c>
       <c r="E832">
         <v>1.6</v>
       </c>
@@ -29894,9 +29491,6 @@
       <c r="B833">
         <v>2</v>
       </c>
-      <c r="D833">
-        <v>0</v>
-      </c>
       <c r="E833">
         <v>2</v>
       </c>
@@ -29914,9 +29508,6 @@
       <c r="B834">
         <v>1.9</v>
       </c>
-      <c r="D834">
-        <v>0</v>
-      </c>
       <c r="E834">
         <v>1.9</v>
       </c>
@@ -29934,9 +29525,6 @@
       <c r="B835">
         <v>1.8</v>
       </c>
-      <c r="D835">
-        <v>0</v>
-      </c>
       <c r="E835">
         <v>1.8</v>
       </c>
@@ -29954,9 +29542,6 @@
       <c r="B836">
         <v>1.7</v>
       </c>
-      <c r="D836">
-        <v>0</v>
-      </c>
       <c r="E836">
         <v>1.7</v>
       </c>
@@ -29974,9 +29559,6 @@
       <c r="B837">
         <v>1.7</v>
       </c>
-      <c r="D837">
-        <v>0</v>
-      </c>
       <c r="E837">
         <v>1.7</v>
       </c>
@@ -29994,9 +29576,6 @@
       <c r="B838">
         <v>1.4</v>
       </c>
-      <c r="D838">
-        <v>0</v>
-      </c>
       <c r="E838">
         <v>1.4</v>
       </c>
@@ -30014,9 +29593,6 @@
       <c r="B839">
         <v>1.3</v>
       </c>
-      <c r="D839">
-        <v>0</v>
-      </c>
       <c r="E839">
         <v>1.3</v>
       </c>
@@ -30034,9 +29610,6 @@
       <c r="B840">
         <v>1.2</v>
       </c>
-      <c r="D840">
-        <v>0</v>
-      </c>
       <c r="E840">
         <v>1.2</v>
       </c>
@@ -30054,9 +29627,6 @@
       <c r="B841">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D841">
-        <v>0</v>
-      </c>
       <c r="E841">
         <v>1.1000000000000001</v>
       </c>
@@ -30074,9 +29644,6 @@
       <c r="B842">
         <v>1.9</v>
       </c>
-      <c r="D842">
-        <v>0</v>
-      </c>
       <c r="E842">
         <v>1.9</v>
       </c>
@@ -30094,9 +29661,6 @@
       <c r="B843">
         <v>1.7</v>
       </c>
-      <c r="D843">
-        <v>0</v>
-      </c>
       <c r="E843">
         <v>1.7</v>
       </c>
@@ -30114,9 +29678,6 @@
       <c r="B844">
         <v>1.5</v>
       </c>
-      <c r="D844">
-        <v>0</v>
-      </c>
       <c r="E844">
         <v>1.5</v>
       </c>
@@ -30134,9 +29695,6 @@
       <c r="B845">
         <v>1.4</v>
       </c>
-      <c r="D845">
-        <v>0</v>
-      </c>
       <c r="E845">
         <v>1.4</v>
       </c>
@@ -30154,9 +29712,6 @@
       <c r="B846">
         <v>1.6</v>
       </c>
-      <c r="D846">
-        <v>0</v>
-      </c>
       <c r="E846">
         <v>1.6</v>
       </c>
@@ -30174,9 +29729,6 @@
       <c r="B847">
         <v>1.8</v>
       </c>
-      <c r="D847">
-        <v>0</v>
-      </c>
       <c r="E847">
         <v>1.8</v>
       </c>
@@ -30194,9 +29746,6 @@
       <c r="B848">
         <v>1.5</v>
       </c>
-      <c r="D848">
-        <v>0</v>
-      </c>
       <c r="E848">
         <v>1.5</v>
       </c>
@@ -30214,9 +29763,6 @@
       <c r="B849">
         <v>1.9</v>
       </c>
-      <c r="D849">
-        <v>0</v>
-      </c>
       <c r="E849">
         <v>1.9</v>
       </c>
@@ -30234,9 +29780,6 @@
       <c r="B850">
         <v>1.6</v>
       </c>
-      <c r="D850">
-        <v>0</v>
-      </c>
       <c r="E850">
         <v>1.6</v>
       </c>
@@ -30254,9 +29797,6 @@
       <c r="B851">
         <v>1.6</v>
       </c>
-      <c r="D851">
-        <v>0</v>
-      </c>
       <c r="E851">
         <v>1.6</v>
       </c>
@@ -30274,9 +29814,6 @@
       <c r="B852">
         <v>1.7</v>
       </c>
-      <c r="D852">
-        <v>0</v>
-      </c>
       <c r="E852">
         <v>1.7</v>
       </c>
@@ -30294,9 +29831,6 @@
       <c r="B853">
         <v>1.7</v>
       </c>
-      <c r="D853">
-        <v>0</v>
-      </c>
       <c r="E853">
         <v>1.7</v>
       </c>
@@ -30314,9 +29848,6 @@
       <c r="B854">
         <v>2.8</v>
       </c>
-      <c r="D854">
-        <v>0</v>
-      </c>
       <c r="E854">
         <v>2.8</v>
       </c>
@@ -30334,9 +29865,6 @@
       <c r="B855">
         <v>3.4</v>
       </c>
-      <c r="D855">
-        <v>0</v>
-      </c>
       <c r="E855">
         <v>3.4</v>
       </c>
@@ -30354,9 +29882,6 @@
       <c r="B856">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D856">
-        <v>0</v>
-      </c>
       <c r="E856">
         <v>2.2000000000000002</v>
       </c>
@@ -30374,9 +29899,6 @@
       <c r="B857">
         <v>1.6</v>
       </c>
-      <c r="D857">
-        <v>0</v>
-      </c>
       <c r="E857">
         <v>1.6</v>
       </c>
@@ -30394,9 +29916,6 @@
       <c r="B858">
         <v>1.5</v>
       </c>
-      <c r="D858">
-        <v>0</v>
-      </c>
       <c r="E858">
         <v>1.5</v>
       </c>
@@ -30414,9 +29933,6 @@
       <c r="B859">
         <v>1.8</v>
       </c>
-      <c r="D859">
-        <v>0</v>
-      </c>
       <c r="E859">
         <v>1.8</v>
       </c>
@@ -30434,9 +29950,6 @@
       <c r="B860">
         <v>1.7</v>
       </c>
-      <c r="D860">
-        <v>0</v>
-      </c>
       <c r="E860">
         <v>1.7</v>
       </c>
@@ -30454,9 +29967,6 @@
       <c r="B861">
         <v>1.3</v>
       </c>
-      <c r="D861">
-        <v>0</v>
-      </c>
       <c r="E861">
         <v>1.3</v>
       </c>
@@ -30474,9 +29984,6 @@
       <c r="B862">
         <v>1.4</v>
       </c>
-      <c r="D862">
-        <v>0</v>
-      </c>
       <c r="E862">
         <v>1.4</v>
       </c>
@@ -30494,9 +30001,6 @@
       <c r="B863">
         <v>1.4</v>
       </c>
-      <c r="D863">
-        <v>0</v>
-      </c>
       <c r="E863">
         <v>1.4</v>
       </c>
@@ -30514,9 +30018,6 @@
       <c r="B864">
         <v>1.3</v>
       </c>
-      <c r="D864">
-        <v>0</v>
-      </c>
       <c r="E864">
         <v>1.3</v>
       </c>
@@ -30534,9 +30035,6 @@
       <c r="B865">
         <v>1</v>
       </c>
-      <c r="D865">
-        <v>0</v>
-      </c>
       <c r="E865">
         <v>1</v>
       </c>
@@ -30557,9 +30055,6 @@
       <c r="C866" t="s">
         <v>67</v>
       </c>
-      <c r="D866">
-        <v>0</v>
-      </c>
       <c r="E866">
         <v>2.6</v>
       </c>
@@ -30577,9 +30072,6 @@
       <c r="B867">
         <v>1.8</v>
       </c>
-      <c r="D867">
-        <v>0</v>
-      </c>
       <c r="E867">
         <v>1.8</v>
       </c>
@@ -30600,9 +30092,6 @@
       <c r="C868" t="s">
         <v>74</v>
       </c>
-      <c r="D868">
-        <v>0</v>
-      </c>
       <c r="E868">
         <v>2</v>
       </c>
@@ -30620,9 +30109,6 @@
       <c r="B869">
         <v>1.8</v>
       </c>
-      <c r="D869">
-        <v>0</v>
-      </c>
       <c r="E869">
         <v>1.8</v>
       </c>
@@ -30640,9 +30126,6 @@
       <c r="B870">
         <v>1.6</v>
       </c>
-      <c r="D870">
-        <v>0</v>
-      </c>
       <c r="E870">
         <v>1.6</v>
       </c>
@@ -30660,9 +30143,6 @@
       <c r="B871">
         <v>1.7</v>
       </c>
-      <c r="D871">
-        <v>0</v>
-      </c>
       <c r="E871">
         <v>1.7</v>
       </c>
@@ -30680,9 +30160,6 @@
       <c r="B872">
         <v>1.6</v>
       </c>
-      <c r="D872">
-        <v>0</v>
-      </c>
       <c r="E872">
         <v>1.6</v>
       </c>
@@ -30700,9 +30177,6 @@
       <c r="B873">
         <v>1.6</v>
       </c>
-      <c r="D873">
-        <v>0</v>
-      </c>
       <c r="E873">
         <v>1.6</v>
       </c>
@@ -30720,9 +30194,6 @@
       <c r="B874">
         <v>1.8</v>
       </c>
-      <c r="D874">
-        <v>0</v>
-      </c>
       <c r="E874">
         <v>1.8</v>
       </c>
@@ -30740,9 +30211,6 @@
       <c r="B875">
         <v>1.5</v>
       </c>
-      <c r="D875">
-        <v>0</v>
-      </c>
       <c r="E875">
         <v>1.5</v>
       </c>
@@ -30760,9 +30228,6 @@
       <c r="B876">
         <v>1.6</v>
       </c>
-      <c r="D876">
-        <v>0</v>
-      </c>
       <c r="E876">
         <v>1.6</v>
       </c>
@@ -30780,9 +30245,6 @@
       <c r="B877">
         <v>1.5</v>
       </c>
-      <c r="D877">
-        <v>0</v>
-      </c>
       <c r="E877">
         <v>1.5</v>
       </c>
@@ -30800,9 +30262,6 @@
       <c r="B878">
         <v>2</v>
       </c>
-      <c r="D878">
-        <v>0</v>
-      </c>
       <c r="E878">
         <v>2</v>
       </c>
@@ -30823,9 +30282,6 @@
       <c r="C879" t="s">
         <v>78</v>
       </c>
-      <c r="D879">
-        <v>0</v>
-      </c>
       <c r="E879">
         <v>1.8</v>
       </c>
@@ -30843,9 +30299,6 @@
       <c r="B880">
         <v>2.9</v>
       </c>
-      <c r="D880">
-        <v>0</v>
-      </c>
       <c r="E880">
         <v>2.9</v>
       </c>
@@ -30863,9 +30316,6 @@
       <c r="B881">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D881">
-        <v>0</v>
-      </c>
       <c r="E881">
         <v>4.4000000000000004</v>
       </c>
@@ -30883,9 +30333,6 @@
       <c r="B882">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D882">
-        <v>0</v>
-      </c>
       <c r="E882">
         <v>4.0999999999999996</v>
       </c>
@@ -30903,9 +30350,6 @@
       <c r="B883">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D883">
-        <v>0</v>
-      </c>
       <c r="E883">
         <v>4.0999999999999996</v>
       </c>
@@ -30923,9 +30367,6 @@
       <c r="B884">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D884">
-        <v>0</v>
-      </c>
       <c r="E884">
         <v>4.0999999999999996</v>
       </c>
@@ -30943,9 +30384,6 @@
       <c r="B885">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D885">
-        <v>0</v>
-      </c>
       <c r="E885">
         <v>4.0999999999999996</v>
       </c>
@@ -30963,9 +30401,6 @@
       <c r="B886">
         <v>4</v>
       </c>
-      <c r="D886">
-        <v>0</v>
-      </c>
       <c r="E886">
         <v>4</v>
       </c>
@@ -30983,9 +30418,6 @@
       <c r="B887">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D887">
-        <v>0</v>
-      </c>
       <c r="E887">
         <v>4.0999999999999996</v>
       </c>
@@ -31003,9 +30435,6 @@
       <c r="B888">
         <v>3.9</v>
       </c>
-      <c r="D888">
-        <v>0</v>
-      </c>
       <c r="E888">
         <v>3.9</v>
       </c>
@@ -31023,9 +30452,6 @@
       <c r="B889">
         <v>4.3</v>
       </c>
-      <c r="D889">
-        <v>0</v>
-      </c>
       <c r="E889">
         <v>4.3</v>
       </c>
@@ -31043,9 +30469,6 @@
       <c r="B890">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D890">
-        <v>0</v>
-      </c>
       <c r="E890">
         <v>4.0999999999999996</v>
       </c>
@@ -31063,9 +30486,6 @@
       <c r="B891">
         <v>4</v>
       </c>
-      <c r="D891">
-        <v>0</v>
-      </c>
       <c r="E891">
         <v>4</v>
       </c>
@@ -31086,9 +30506,6 @@
       <c r="C892" t="s">
         <v>85</v>
       </c>
-      <c r="D892">
-        <v>0</v>
-      </c>
       <c r="E892">
         <v>3.8</v>
       </c>
@@ -31106,9 +30523,6 @@
       <c r="B893">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D893">
-        <v>0</v>
-      </c>
       <c r="E893">
         <v>4.0999999999999996</v>
       </c>
@@ -31126,9 +30540,6 @@
       <c r="B894">
         <v>4</v>
       </c>
-      <c r="D894">
-        <v>0</v>
-      </c>
       <c r="E894">
         <v>4</v>
       </c>
@@ -31146,9 +30557,6 @@
       <c r="B895">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D895">
-        <v>0</v>
-      </c>
       <c r="E895">
         <v>4.0999999999999996</v>
       </c>
@@ -31166,9 +30574,6 @@
       <c r="B896">
         <v>3.6</v>
       </c>
-      <c r="D896">
-        <v>0</v>
-      </c>
       <c r="E896">
         <v>3.6</v>
       </c>
@@ -31186,9 +30591,6 @@
       <c r="B897">
         <v>3.9</v>
       </c>
-      <c r="D897">
-        <v>0</v>
-      </c>
       <c r="E897">
         <v>3.9</v>
       </c>
@@ -31206,9 +30608,6 @@
       <c r="B898">
         <v>3.7</v>
       </c>
-      <c r="D898">
-        <v>0</v>
-      </c>
       <c r="E898">
         <v>3.7</v>
       </c>
@@ -31226,9 +30625,6 @@
       <c r="B899">
         <v>3.7</v>
       </c>
-      <c r="D899">
-        <v>0</v>
-      </c>
       <c r="E899">
         <v>3.7</v>
       </c>
@@ -31246,9 +30642,6 @@
       <c r="B900">
         <v>3.6</v>
       </c>
-      <c r="D900">
-        <v>0</v>
-      </c>
       <c r="E900">
         <v>3.6</v>
       </c>
@@ -31269,9 +30662,6 @@
       <c r="C901" t="s">
         <v>91</v>
       </c>
-      <c r="D901">
-        <v>0</v>
-      </c>
       <c r="E901">
         <v>3.6</v>
       </c>
@@ -31292,9 +30682,6 @@
       <c r="C902" t="s">
         <v>97</v>
       </c>
-      <c r="D902">
-        <v>0</v>
-      </c>
       <c r="E902">
         <v>3.7</v>
       </c>
@@ -31312,9 +30699,6 @@
       <c r="B903">
         <v>3.4</v>
       </c>
-      <c r="D903">
-        <v>0</v>
-      </c>
       <c r="E903">
         <v>3.4</v>
       </c>
@@ -31335,9 +30719,6 @@
       <c r="C904" t="s">
         <v>103</v>
       </c>
-      <c r="D904">
-        <v>0</v>
-      </c>
       <c r="E904">
         <v>3.6</v>
       </c>
@@ -31355,9 +30736,6 @@
       <c r="B905">
         <v>3.8</v>
       </c>
-      <c r="D905">
-        <v>0</v>
-      </c>
       <c r="E905">
         <v>3.8</v>
       </c>
@@ -31375,9 +30753,6 @@
       <c r="B906">
         <v>3.6</v>
       </c>
-      <c r="D906">
-        <v>0</v>
-      </c>
       <c r="E906">
         <v>3.6</v>
       </c>
@@ -31395,9 +30770,6 @@
       <c r="B907">
         <v>3.5</v>
       </c>
-      <c r="D907">
-        <v>0</v>
-      </c>
       <c r="E907">
         <v>3.5</v>
       </c>
@@ -31415,9 +30787,6 @@
       <c r="B908">
         <v>3.5</v>
       </c>
-      <c r="D908">
-        <v>0</v>
-      </c>
       <c r="E908">
         <v>3.5</v>
       </c>
@@ -31430,6 +30799,3451 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E78A6AD-F7E1-4B1E-B9FD-88C854ADE73D}">
+  <sheetPr>
+    <tabColor rgb="FFCCFF33"/>
+  </sheetPr>
+  <dimension ref="A1:D325"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1950.03</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.51354299999999997</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.51354299999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>1950.08</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.72190900000000002</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.75704585995744056</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>1950.11</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.94341600000000003</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1.1093725198521249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>1950.2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1.2097100000000001</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1.3903823655241381</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>1950.38</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1.8086599999999999</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.7270944510541251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>1950.59</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1.6778</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.803151034958292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>1950.74</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1.4623200000000001</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1.757510657656933</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>1950.89</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1.238</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.68509628555894</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>1950.95</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1.0438499999999999</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.578987316219961</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>1951.05</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.0711999999999999</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.4504647878730541</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>1951.18</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1.4042600000000001</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.3358826592912481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>1951.32</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1.3789199999999999</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.1616573740675089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>1951.67</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.99704999999999999</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.0711999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>1951.82</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.73732900000000001</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.206497777242679</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>1951.95</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.83145599999999997</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.3965272467791621</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>1952.14</v>
+      </c>
+      <c r="B17" s="6">
+        <v>2.16492</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.3967900795749091</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>1952.3</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2.1309999999999998</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.3753804141731509</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>1952.64</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1.7888200000000001</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.320815002718609</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>1952.8</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1.4495800000000001</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.232586018823786</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>1952.94</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1.49061</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.1199356043037509</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>1953.09</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1.89019</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.0008245962414051</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>1953.26</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1.9536100000000001</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.8321449458623581</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>1953.85</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1.28627</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.73787329440999982</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>1954.17</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1.46608</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.78223346986131936</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>1954.24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1.3163</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2.16492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>1954.41</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1.25583</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2.16492</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>1954.79</v>
+      </c>
+      <c r="B28" s="6">
+        <v>0.39635300000000001</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.1637789529322369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>1955.23</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1.87812</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2.1464335909664731</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>1955.53</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1.68611</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="6">
+        <v>2.1173583135798162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>1955.64</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1.4702299999999999</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.0578582099449449</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>1955.8</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1.17082</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1.973092941523054</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>1955.92</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1.1630499999999999</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1.865380669716741</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>1956.03</v>
+      </c>
+      <c r="B34" s="6">
+        <v>1.28345</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1.7285274306977909</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>1956.18</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1.49718</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.506120447323956</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>1956.2</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1.64334</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1.450380710628129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>1956.29</v>
+      </c>
+      <c r="B37" s="6">
+        <v>1.6485700000000001</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1.4744370459717799</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>1956.52</v>
+      </c>
+      <c r="B38" s="6">
+        <v>1.4558899999999999</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1.89019</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>1956.8</v>
+      </c>
+      <c r="B39" s="6">
+        <v>1.0557799999999999</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1.89019</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>1957.12</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1.8727499999999999</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1.9324895889503531</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>1957.29</v>
+      </c>
+      <c r="B41" s="6">
+        <v>1.91405</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1.953320497661643</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>1957.68</v>
+      </c>
+      <c r="B42" s="6">
+        <v>1.52373</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1.9442319873710121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>1957.77</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1.24135</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1.9083090059560901</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>1957.88</v>
+      </c>
+      <c r="B44" s="6">
+        <v>1.15822</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1.847560370035948</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>1958.11</v>
+      </c>
+      <c r="B45" s="6">
+        <v>2.1735000000000002</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1.7575418836484611</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>1958.5</v>
+      </c>
+      <c r="B46" s="6">
+        <v>1.9115</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1.6394311130655239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>1958.52</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1.7788999999999999</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1.498001203077288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>1958.67</v>
+      </c>
+      <c r="B48" s="6">
+        <v>1.70059</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="6">
+        <v>1.323429206117086</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>1958.7</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1.43537</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1.28627</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>1958.79</v>
+      </c>
+      <c r="B50" s="6">
+        <v>1.4538800000000001</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1.46608</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>1958.92</v>
+      </c>
+      <c r="B51" s="6">
+        <v>1.36216</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1.46608</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>1959.11</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1.8150999999999999</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1.46608</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>1959.41</v>
+      </c>
+      <c r="B53" s="6">
+        <v>1.5478700000000001</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1.3110264723159499</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>1959.67</v>
+      </c>
+      <c r="B54" s="6">
+        <v>1.14307</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1.2823204853596419</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>1959.8</v>
+      </c>
+      <c r="B55" s="6">
+        <v>0.91418600000000005</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1.2525836061255771</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>1959.89</v>
+      </c>
+      <c r="B56" s="6">
+        <v>0.95923800000000004</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1.166404096844694</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>1959.94</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1.11893</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1.009930285763476</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>1960.11</v>
+      </c>
+      <c r="B58" s="6">
+        <v>1.0496099999999999</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.79444843783937813</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>1960.21</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1.1080700000000001</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.53879735552379526</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>1960.33</v>
+      </c>
+      <c r="B60" s="6">
+        <v>0</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1.46608</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>1960.77</v>
+      </c>
+      <c r="B61" s="6">
+        <v>0</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.39635300000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>1960.82</v>
+      </c>
+      <c r="B62" s="6">
+        <v>0.52051499999999995</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="6">
+        <v>1.87812</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>1961.05</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1.42961</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D63" s="6">
+        <v>1.87812</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>1961.48</v>
+      </c>
+      <c r="B64" s="6">
+        <v>0.87154699999999996</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D64" s="6">
+        <v>1.87812</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>1961.68</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1.1874499999999999</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" s="6">
+        <v>1.8770816314984149</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="7">
+        <v>1961.86</v>
+      </c>
+      <c r="B66" s="8">
+        <v>0.97666900000000001</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" s="6">
+        <v>1.851231577241552</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>1961.97</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1.0041599999999999</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" s="6">
+        <v>1.7947077788486581</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>1962.14</v>
+      </c>
+      <c r="B68" s="6">
+        <v>1.5233300000000001</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D68" s="6">
+        <v>1.719762490170663</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>1962.27</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1.5289600000000001</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D69" s="6">
+        <v>1.5962880582532151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>1962.38</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1.55202</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D70" s="6">
+        <v>1.410873716196873</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>1962.55</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1.1906699999999999</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1.2218791727083911</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>1962.83</v>
+      </c>
+      <c r="B72" s="6">
+        <v>0.94542800000000005</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" s="6">
+        <v>1.167072585532491</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>1963.15</v>
+      </c>
+      <c r="B73" s="6">
+        <v>1.7535499999999999</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D73" s="6">
+        <v>1.1630545836867161</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>1963.24</v>
+      </c>
+      <c r="B74" s="6">
+        <v>1.78976</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D74" s="6">
+        <v>1.28345</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>1963.71</v>
+      </c>
+      <c r="B75" s="6">
+        <v>1.1390499999999999</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" s="6">
+        <v>1.315249417840854</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>1963.83</v>
+      </c>
+      <c r="B76" s="6">
+        <v>1.09145</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D76" s="6">
+        <v>1.4606205467224309</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>1963.86</v>
+      </c>
+      <c r="B77" s="6">
+        <v>1.6359600000000001</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D77" s="6">
+        <v>1.647831852371733</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>1964.05</v>
+      </c>
+      <c r="B78" s="6">
+        <v>1.8012900000000001</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D78" s="6">
+        <v>1.637343179120254</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>1964.76</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1.0907800000000001</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D79" s="6">
+        <v>1.56835889059592</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>1964.95</v>
+      </c>
+      <c r="B80" s="6">
+        <v>1.3712800000000001</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D80" s="6">
+        <v>1.4765656980012449</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>1965.15</v>
+      </c>
+      <c r="B81" s="6">
+        <v>1.47479</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" s="6">
+        <v>1.3803692210650369</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>1965.42</v>
+      </c>
+      <c r="B82" s="6">
+        <v>1.36216</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D82" s="6">
+        <v>1.2646366668457829</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>1965.64</v>
+      </c>
+      <c r="B83" s="6">
+        <v>1.06758</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D83" s="6">
+        <v>1.135494185445159</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>1965.74</v>
+      </c>
+      <c r="B84" s="6">
+        <v>0.68356099999999997</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" s="6">
+        <v>1.28345</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>1965.98</v>
+      </c>
+      <c r="B85" s="6">
+        <v>0.85827299999999995</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D85" s="6">
+        <v>1.0557799999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>1966.05</v>
+      </c>
+      <c r="B86" s="6">
+        <v>1.02695</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D86" s="6">
+        <v>1.8727499999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>1966.14</v>
+      </c>
+      <c r="B87" s="6">
+        <v>1.0896999999999999</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D87" s="6">
+        <v>1.8727499999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>1966.44</v>
+      </c>
+      <c r="B88" s="6">
+        <v>0.747251</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" s="6">
+        <v>1.8944937991630051</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>1966.59</v>
+      </c>
+      <c r="B89" s="6">
+        <v>0.32823799999999997</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D89" s="6">
+        <v>1.9126252951405309</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>1966.71</v>
+      </c>
+      <c r="B90" s="6">
+        <v>0.271789</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D90" s="6">
+        <v>1.9085985522233651</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>1966.85</v>
+      </c>
+      <c r="B91" s="6">
+        <v>0.45883600000000002</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D91" s="6">
+        <v>1.865416851639019</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>1966.94</v>
+      </c>
+      <c r="B92" s="6">
+        <v>0.42424200000000001</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D92" s="6">
+        <v>1.788256993805184</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>1967.17</v>
+      </c>
+      <c r="B93" s="6">
+        <v>0.908555</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D93" s="6">
+        <v>1.678962642685103</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>1967.29</v>
+      </c>
+      <c r="B94" s="6">
+        <v>0.94060100000000002</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D94" s="6">
+        <v>1.5467233686231141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>1967.61</v>
+      </c>
+      <c r="B95" s="6">
+        <v>0.48766399999999999</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D95" s="6">
+        <v>1.291935619326027</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>1967.62</v>
+      </c>
+      <c r="B96" s="6">
+        <v>0</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D96" s="6">
+        <v>1.1763337701770991</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>1967.89</v>
+      </c>
+      <c r="B97" s="6">
+        <v>0</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D97" s="6">
+        <v>1.15822</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>1967.89</v>
+      </c>
+      <c r="B98" s="6">
+        <v>0.2203</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D98" s="6">
+        <v>2.1735000000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>1968.06</v>
+      </c>
+      <c r="B99" s="6">
+        <v>0.243899</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D99" s="6">
+        <v>2.1735000000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>1968.12</v>
+      </c>
+      <c r="B100" s="6">
+        <v>0</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D100" s="6">
+        <v>2.1705353937924539</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>1968.73</v>
+      </c>
+      <c r="B101" s="6">
+        <v>0</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D101" s="6">
+        <v>2.1499569110631498</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>1968.89</v>
+      </c>
+      <c r="B102" s="6">
+        <v>1.1317999999999999</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D102" s="6">
+        <v>2.1057662806240951</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>1969.08</v>
+      </c>
+      <c r="B103" s="6">
+        <v>1.29271</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D103" s="6">
+        <v>2.028254832009301</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>1969.5</v>
+      </c>
+      <c r="B104" s="6">
+        <v>0.92477900000000002</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D104" s="6">
+        <v>1.915949960349512</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>1969.61</v>
+      </c>
+      <c r="B105" s="6">
+        <v>0.56730999999999998</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D105" s="6">
+        <v>1.7415139284031029</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>1969.77</v>
+      </c>
+      <c r="B106" s="6">
+        <v>0.55993599999999999</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D106" s="6">
+        <v>1.703835572094538</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>1969.88</v>
+      </c>
+      <c r="B107" s="6">
+        <v>1.3307899999999999</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D107" s="6">
+        <v>1.445883568745304</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>1969.97</v>
+      </c>
+      <c r="B108" s="6">
+        <v>1.4068099999999999</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D108" s="6">
+        <v>1.4415425020239869</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>1970.35</v>
+      </c>
+      <c r="B109" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D109" s="6">
+        <v>1.3655660193060219</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>1970.52</v>
+      </c>
+      <c r="B110" s="6">
+        <v>0.83199199999999995</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D110" s="6">
+        <v>1.8150999999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>1970.61</v>
+      </c>
+      <c r="B111" s="6">
+        <v>0.50536300000000001</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D111" s="6">
+        <v>1.8150999999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>1970.76</v>
+      </c>
+      <c r="B112" s="6">
+        <v>0.78988999999999998</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D112" s="6">
+        <v>1.7829018207279781</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>1970.97</v>
+      </c>
+      <c r="B113" s="6">
+        <v>1.7696400000000001</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D113" s="6">
+        <v>1.7151242559679909</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>1971.36</v>
+      </c>
+      <c r="B114" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D114" s="6">
+        <v>1.6350676697888871</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>1971.67</v>
+      </c>
+      <c r="B115" s="6">
+        <v>0.75811200000000001</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D115" s="6">
+        <v>1.5415254307848789</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" s="7">
+        <v>1971.86</v>
+      </c>
+      <c r="B116" s="8">
+        <v>0.78640399999999999</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="6">
+        <v>1.429684970103092</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>1971.98</v>
+      </c>
+      <c r="B117" s="6">
+        <v>1.2476499999999999</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D117" s="6">
+        <v>1.291978210910204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>1972.09</v>
+      </c>
+      <c r="B118" s="6">
+        <v>1.24417</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D118" s="6">
+        <v>1.1476546625095849</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>1972.47</v>
+      </c>
+      <c r="B119" s="6">
+        <v>0.791767</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D119" s="6">
+        <v>0.96970587619619142</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>1972.73</v>
+      </c>
+      <c r="B120" s="6">
+        <v>0</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D120" s="6">
+        <v>0.9218577221459282</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>1973.76</v>
+      </c>
+      <c r="B121" s="6">
+        <v>0</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D121" s="6">
+        <v>1.0236500140800091</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>1974</v>
+      </c>
+      <c r="B122" s="9">
+        <v>1.14602</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D122" s="6">
+        <v>1.0496099999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>1974.23</v>
+      </c>
+      <c r="B123" s="9">
+        <v>2.2586499999999998</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D123" s="6">
+        <v>1.0496099999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>1974.35</v>
+      </c>
+      <c r="B124" s="9">
+        <v>2.0207799999999998</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D124" s="6">
+        <v>1.102937709190672</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>1974.53</v>
+      </c>
+      <c r="B125" s="9">
+        <v>2.0887600000000002</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D125" s="6">
+        <v>0.80953733541510142</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>1974.61</v>
+      </c>
+      <c r="B126" s="9">
+        <v>1.8460700000000001</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D126" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <v>1974.79</v>
+      </c>
+      <c r="B127" s="9">
+        <v>1.7813099999999999</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D127" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <v>1974.92</v>
+      </c>
+      <c r="B128" s="9">
+        <v>1.8002100000000001</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D128" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <v>1975</v>
+      </c>
+      <c r="B129" s="6">
+        <v>1.9867300000000001</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>1975.09</v>
+      </c>
+      <c r="B130" s="6">
+        <v>1.9477100000000001</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D130" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>1975.44</v>
+      </c>
+      <c r="B131" s="6">
+        <v>1.5437099999999999</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D131" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>1975.64</v>
+      </c>
+      <c r="B132" s="6">
+        <v>1.16492</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D132" s="6">
+        <v>1.0496099999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>1975.74</v>
+      </c>
+      <c r="B133" s="6">
+        <v>1.1260399999999999</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D133" s="6">
+        <v>0.52051499999999995</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>1975.85</v>
+      </c>
+      <c r="B134" s="6">
+        <v>1.3216699999999999</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D134" s="6">
+        <v>1.42961</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>1976.06</v>
+      </c>
+      <c r="B135" s="6">
+        <v>1.9253199999999999</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D135" s="6">
+        <v>1.3210510828718229</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>1976.15</v>
+      </c>
+      <c r="B136" s="6">
+        <v>2.5146199999999999</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D136" s="6">
+        <v>1.1353316420513031</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A137">
+        <v>1976.44</v>
+      </c>
+      <c r="B137" s="6">
+        <v>2.3976899999999999</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D137" s="6">
+        <v>0.99659229316564057</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A138">
+        <v>1976.59</v>
+      </c>
+      <c r="B138" s="6">
+        <v>2.06718</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D138" s="6">
+        <v>0.91717969565583624</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A139">
+        <v>1976.74</v>
+      </c>
+      <c r="B139" s="6">
+        <v>1.94462</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D139" s="6">
+        <v>0.87891346380898094</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C140" t="s">
+        <v>288</v>
+      </c>
+      <c r="D140" s="6">
+        <v>0.87759843003005011</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C141" t="s">
+        <v>289</v>
+      </c>
+      <c r="D141" s="6">
+        <v>1.0327438757535019</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C142" t="s">
+        <v>290</v>
+      </c>
+      <c r="D142" s="6">
+        <v>1.1832070153103851</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D143" s="6">
+        <v>1.117893229403732</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C144" t="s">
+        <v>292</v>
+      </c>
+      <c r="D144" s="6">
+        <v>0.98767297704870272</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C145" t="s">
+        <v>293</v>
+      </c>
+      <c r="D145" s="6">
+        <v>0.9803629996662846</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C146" t="s">
+        <v>294</v>
+      </c>
+      <c r="D146" s="6">
+        <v>1.5233300000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C147" t="s">
+        <v>295</v>
+      </c>
+      <c r="D147" s="6">
+        <v>1.5233300000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C148" t="s">
+        <v>296</v>
+      </c>
+      <c r="D148" s="6">
+        <v>1.5235356716207229</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C149" t="s">
+        <v>297</v>
+      </c>
+      <c r="D149" s="6">
+        <v>1.527413984596925</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C150" t="s">
+        <v>298</v>
+      </c>
+      <c r="D150" s="6">
+        <v>1.543113247445089</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C151" t="s">
+        <v>299</v>
+      </c>
+      <c r="D151" s="6">
+        <v>1.5186126757841321</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C152" t="s">
+        <v>300</v>
+      </c>
+      <c r="D152" s="6">
+        <v>1.3038780764313</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C153" t="s">
+        <v>301</v>
+      </c>
+      <c r="D153" s="6">
+        <v>1.148710173631996</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C154" t="s">
+        <v>302</v>
+      </c>
+      <c r="D154" s="6">
+        <v>1.048854462359752</v>
+      </c>
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C155" t="s">
+        <v>303</v>
+      </c>
+      <c r="D155" s="6">
+        <v>0.97691852043211502</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C156" t="s">
+        <v>304</v>
+      </c>
+      <c r="D156" s="6">
+        <v>1.5233300000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C157" t="s">
+        <v>305</v>
+      </c>
+      <c r="D157" s="6">
+        <v>0.94542800000000005</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C158" t="s">
+        <v>306</v>
+      </c>
+      <c r="D158" s="6">
+        <v>1.7535499999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C159" t="s">
+        <v>307</v>
+      </c>
+      <c r="D159" s="6">
+        <v>1.7535499999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C160" t="s">
+        <v>308</v>
+      </c>
+      <c r="D160" s="6">
+        <v>1.7625696848194869</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C161" t="s">
+        <v>309</v>
+      </c>
+      <c r="D161" s="6">
+        <v>1.7892524033254851</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C162" t="s">
+        <v>310</v>
+      </c>
+      <c r="D162" s="6">
+        <v>1.7349916208671179</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C163" t="s">
+        <v>311</v>
+      </c>
+      <c r="D163" s="6">
+        <v>1.609611726351591</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C164" t="s">
+        <v>312</v>
+      </c>
+      <c r="D164" s="6">
+        <v>1.455103208410264</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C165" t="s">
+        <v>313</v>
+      </c>
+      <c r="D165" s="6">
+        <v>1.2965819728015451</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C166" t="s">
+        <v>314</v>
+      </c>
+      <c r="D166" s="6">
+        <v>1.175214023633472</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C167" t="s">
+        <v>315</v>
+      </c>
+      <c r="D167" s="6">
+        <v>1.117367713171034</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C168" t="s">
+        <v>316</v>
+      </c>
+      <c r="D168" s="6">
+        <v>1.1211107291830471</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C169" t="s">
+        <v>317</v>
+      </c>
+      <c r="D169" s="6">
+        <v>1.6359600000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C170" t="s">
+        <v>318</v>
+      </c>
+      <c r="D170" s="6">
+        <v>1.8012900000000001</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C171" t="s">
+        <v>319</v>
+      </c>
+      <c r="D171" s="6">
+        <v>1.7008762554486869</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C172" t="s">
+        <v>320</v>
+      </c>
+      <c r="D172" s="6">
+        <v>1.5119117163656539</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C173" t="s">
+        <v>321</v>
+      </c>
+      <c r="D173" s="6">
+        <v>1.3580880126384649</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C174" t="s">
+        <v>322</v>
+      </c>
+      <c r="D174" s="6">
+        <v>1.2501577491795499</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C175" t="s">
+        <v>323</v>
+      </c>
+      <c r="D175" s="6">
+        <v>1.1740971419701129</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C176" t="s">
+        <v>324</v>
+      </c>
+      <c r="D176" s="6">
+        <v>1.1282769937116759</v>
+      </c>
+    </row>
+    <row r="177" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C177" t="s">
+        <v>325</v>
+      </c>
+      <c r="D177" s="6">
+        <v>1.102814194732141</v>
+      </c>
+    </row>
+    <row r="178" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C178" t="s">
+        <v>326</v>
+      </c>
+      <c r="D178" s="6">
+        <v>1.0926544740284141</v>
+      </c>
+    </row>
+    <row r="179" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C179" t="s">
+        <v>327</v>
+      </c>
+      <c r="D179" s="6">
+        <v>1.0907848939710449</v>
+      </c>
+    </row>
+    <row r="180" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C180" t="s">
+        <v>328</v>
+      </c>
+      <c r="D180" s="6">
+        <v>1.1547466616118871</v>
+      </c>
+    </row>
+    <row r="181" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C181" t="s">
+        <v>329</v>
+      </c>
+      <c r="D181" s="6">
+        <v>1.30943813322477</v>
+      </c>
+    </row>
+    <row r="182" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C182" t="s">
+        <v>330</v>
+      </c>
+      <c r="D182" s="6">
+        <v>1.47479</v>
+      </c>
+    </row>
+    <row r="183" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C183" t="s">
+        <v>331</v>
+      </c>
+      <c r="D183" s="6">
+        <v>1.47479</v>
+      </c>
+    </row>
+    <row r="184" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C184" t="s">
+        <v>332</v>
+      </c>
+      <c r="D184" s="6">
+        <v>1.474381868335678</v>
+      </c>
+    </row>
+    <row r="185" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C185" t="s">
+        <v>333</v>
+      </c>
+      <c r="D185" s="6">
+        <v>1.455698348058541</v>
+      </c>
+    </row>
+    <row r="186" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C186" t="s">
+        <v>334</v>
+      </c>
+      <c r="D186" s="6">
+        <v>1.417340544002536</v>
+      </c>
+    </row>
+    <row r="187" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C187" t="s">
+        <v>335</v>
+      </c>
+      <c r="D187" s="6">
+        <v>1.3656970983429011</v>
+      </c>
+    </row>
+    <row r="188" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C188" t="s">
+        <v>336</v>
+      </c>
+      <c r="D188" s="6">
+        <v>1.294979023666085</v>
+      </c>
+    </row>
+    <row r="189" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C189" t="s">
+        <v>337</v>
+      </c>
+      <c r="D189" s="6">
+        <v>1.1765534151952419</v>
+      </c>
+    </row>
+    <row r="190" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C190" t="s">
+        <v>338</v>
+      </c>
+      <c r="D190" s="6">
+        <v>0.96784943659467682</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C191" t="s">
+        <v>339</v>
+      </c>
+      <c r="D191" s="6">
+        <v>0.6835681635573414</v>
+      </c>
+    </row>
+    <row r="192" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C192" t="s">
+        <v>340</v>
+      </c>
+      <c r="D192" s="6">
+        <v>0.69398901695360538</v>
+      </c>
+    </row>
+    <row r="193" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C193" t="s">
+        <v>341</v>
+      </c>
+      <c r="D193" s="6">
+        <v>0.75311224354482809</v>
+      </c>
+    </row>
+    <row r="194" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C194" t="s">
+        <v>342</v>
+      </c>
+      <c r="D194" s="6">
+        <v>1.02695</v>
+      </c>
+    </row>
+    <row r="195" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C195" t="s">
+        <v>343</v>
+      </c>
+      <c r="D195" s="6">
+        <v>1.0631679881857969</v>
+      </c>
+    </row>
+    <row r="196" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C196" t="s">
+        <v>344</v>
+      </c>
+      <c r="D196" s="6">
+        <v>1.086972968940549</v>
+      </c>
+    </row>
+    <row r="197" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C197" t="s">
+        <v>345</v>
+      </c>
+      <c r="D197" s="6">
+        <v>1.0313265667786959</v>
+      </c>
+    </row>
+    <row r="198" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C198" t="s">
+        <v>346</v>
+      </c>
+      <c r="D198" s="6">
+        <v>0.9264772468142628</v>
+      </c>
+    </row>
+    <row r="199" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C199" t="s">
+        <v>347</v>
+      </c>
+      <c r="D199" s="6">
+        <v>0.78918242720145293</v>
+      </c>
+    </row>
+    <row r="200" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C200" t="s">
+        <v>348</v>
+      </c>
+      <c r="D200" s="6">
+        <v>0.58383567670628755</v>
+      </c>
+    </row>
+    <row r="201" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C201" t="s">
+        <v>349</v>
+      </c>
+      <c r="D201" s="6">
+        <v>0.33685853191330511</v>
+      </c>
+    </row>
+    <row r="202" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C202" t="s">
+        <v>350</v>
+      </c>
+      <c r="D202" s="6">
+        <v>0.2808313839120441</v>
+      </c>
+    </row>
+    <row r="203" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C203" t="s">
+        <v>351</v>
+      </c>
+      <c r="D203" s="6">
+        <v>0.30633567887916408</v>
+      </c>
+    </row>
+    <row r="204" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C204" t="s">
+        <v>352</v>
+      </c>
+      <c r="D204" s="6">
+        <v>0.45167849216364753</v>
+      </c>
+    </row>
+    <row r="205" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C205" t="s">
+        <v>353</v>
+      </c>
+      <c r="D205" s="6">
+        <v>0.44436740725681712</v>
+      </c>
+    </row>
+    <row r="206" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C206" t="s">
+        <v>354</v>
+      </c>
+      <c r="D206" s="6">
+        <v>0.908555</v>
+      </c>
+    </row>
+    <row r="207" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C207" t="s">
+        <v>355</v>
+      </c>
+      <c r="D207" s="6">
+        <v>0.908555</v>
+      </c>
+    </row>
+    <row r="208" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C208" t="s">
+        <v>356</v>
+      </c>
+      <c r="D208" s="6">
+        <v>0.908555</v>
+      </c>
+    </row>
+    <row r="209" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C209" t="s">
+        <v>357</v>
+      </c>
+      <c r="D209" s="6">
+        <v>0.93838946437626203</v>
+      </c>
+    </row>
+    <row r="210" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C210" t="s">
+        <v>358</v>
+      </c>
+      <c r="D210" s="6">
+        <v>0.93794893868304563</v>
+      </c>
+    </row>
+    <row r="211" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C211" t="s">
+        <v>359</v>
+      </c>
+      <c r="D211" s="6">
+        <v>0.90196138384661972</v>
+      </c>
+    </row>
+    <row r="212" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C212" t="s">
+        <v>360</v>
+      </c>
+      <c r="D212" s="6">
+        <v>0.7989410966952607</v>
+      </c>
+    </row>
+    <row r="213" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C213" t="s">
+        <v>361</v>
+      </c>
+      <c r="D213" s="6">
+        <v>0.58568937882797245</v>
+      </c>
+    </row>
+    <row r="214" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C214" t="s">
+        <v>362</v>
+      </c>
+      <c r="D214" s="6">
+        <v>5.7498039719844623E-4</v>
+      </c>
+    </row>
+    <row r="215" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C215" t="s">
+        <v>363</v>
+      </c>
+      <c r="D215" s="6">
+        <v>1.215065942974441E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C216" t="s">
+        <v>364</v>
+      </c>
+      <c r="D216" s="6">
+        <v>5.5537980348324259E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C217" t="s">
+        <v>365</v>
+      </c>
+      <c r="D217" s="6">
+        <v>0.11015</v>
+      </c>
+    </row>
+    <row r="218" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C218" t="s">
+        <v>366</v>
+      </c>
+      <c r="D218" s="6">
+        <v>0.243899</v>
+      </c>
+    </row>
+    <row r="219" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C219" t="s">
+        <v>367</v>
+      </c>
+      <c r="D219" s="6">
+        <v>0.1025872424906852</v>
+      </c>
+    </row>
+    <row r="220" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C220" t="s">
+        <v>368</v>
+      </c>
+      <c r="D220" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C221" t="s">
+        <v>369</v>
+      </c>
+      <c r="D221" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C222" t="s">
+        <v>370</v>
+      </c>
+      <c r="D222" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C223" t="s">
+        <v>371</v>
+      </c>
+      <c r="D223" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C224" t="s">
+        <v>372</v>
+      </c>
+      <c r="D224" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C225" t="s">
+        <v>373</v>
+      </c>
+      <c r="D225" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C226" t="s">
+        <v>374</v>
+      </c>
+      <c r="D226" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C227" t="s">
+        <v>375</v>
+      </c>
+      <c r="D227" s="6">
+        <v>3.6263529223620299E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C228" t="s">
+        <v>376</v>
+      </c>
+      <c r="D228" s="6">
+        <v>0.64476775512748663</v>
+      </c>
+    </row>
+    <row r="229" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C229" t="s">
+        <v>377</v>
+      </c>
+      <c r="D229" s="6">
+        <v>1.1317999999999999</v>
+      </c>
+    </row>
+    <row r="230" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C230" t="s">
+        <v>378</v>
+      </c>
+      <c r="D230" s="6">
+        <v>1.29271</v>
+      </c>
+    </row>
+    <row r="231" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C231" t="s">
+        <v>379</v>
+      </c>
+      <c r="D231" s="6">
+        <v>1.292633200311236</v>
+      </c>
+    </row>
+    <row r="232" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C232" t="s">
+        <v>380</v>
+      </c>
+      <c r="D232" s="6">
+        <v>1.2760112421702661</v>
+      </c>
+    </row>
+    <row r="233" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C233" t="s">
+        <v>381</v>
+      </c>
+      <c r="D233" s="6">
+        <v>1.226330182817519</v>
+      </c>
+    </row>
+    <row r="234" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C234" t="s">
+        <v>382</v>
+      </c>
+      <c r="D234" s="6">
+        <v>1.150712630816606</v>
+      </c>
+    </row>
+    <row r="235" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C235" t="s">
+        <v>383</v>
+      </c>
+      <c r="D235" s="6">
+        <v>1.0481296255543371</v>
+      </c>
+    </row>
+    <row r="236" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C236" t="s">
+        <v>384</v>
+      </c>
+      <c r="D236" s="6">
+        <v>0.92904000467391568</v>
+      </c>
+    </row>
+    <row r="237" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C237" t="s">
+        <v>385</v>
+      </c>
+      <c r="D237" s="6">
+        <v>0.61663751677134848</v>
+      </c>
+    </row>
+    <row r="238" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C238" t="s">
+        <v>386</v>
+      </c>
+      <c r="D238" s="6">
+        <v>0.56288248669627594</v>
+      </c>
+    </row>
+    <row r="239" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C239" t="s">
+        <v>387</v>
+      </c>
+      <c r="D239" s="6">
+        <v>0.56005947417004176</v>
+      </c>
+    </row>
+    <row r="240" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C240" t="s">
+        <v>388</v>
+      </c>
+      <c r="D240" s="6">
+        <v>1.008870092156436</v>
+      </c>
+    </row>
+    <row r="241" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C241" t="s">
+        <v>389</v>
+      </c>
+      <c r="D241" s="6">
+        <v>1.3760562711554309</v>
+      </c>
+    </row>
+    <row r="242" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C242" t="s">
+        <v>390</v>
+      </c>
+      <c r="D242" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+    </row>
+    <row r="243" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C243" t="s">
+        <v>391</v>
+      </c>
+      <c r="D243" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+    </row>
+    <row r="244" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C244" t="s">
+        <v>392</v>
+      </c>
+      <c r="D244" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+    </row>
+    <row r="245" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C245" t="s">
+        <v>393</v>
+      </c>
+      <c r="D245" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+    </row>
+    <row r="246" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C246" t="s">
+        <v>394</v>
+      </c>
+      <c r="D246" s="6">
+        <v>0.91458799999999996</v>
+      </c>
+    </row>
+    <row r="247" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C247" t="s">
+        <v>395</v>
+      </c>
+      <c r="D247" s="6">
+        <v>0.9015368868512933</v>
+      </c>
+    </row>
+    <row r="248" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C248" t="s">
+        <v>396</v>
+      </c>
+      <c r="D248" s="6">
+        <v>0.85121294196548991</v>
+      </c>
+    </row>
+    <row r="249" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C249" t="s">
+        <v>397</v>
+      </c>
+      <c r="D249" s="6">
+        <v>0.57178853299630461</v>
+      </c>
+    </row>
+    <row r="250" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C250" t="s">
+        <v>398</v>
+      </c>
+      <c r="D250" s="6">
+        <v>0.56250155066339425</v>
+      </c>
+    </row>
+    <row r="251" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C251" t="s">
+        <v>399</v>
+      </c>
+      <c r="D251" s="6">
+        <v>0.7608744435535848</v>
+      </c>
+    </row>
+    <row r="252" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C252" t="s">
+        <v>400</v>
+      </c>
+      <c r="D252" s="6">
+        <v>1.043326315604195</v>
+      </c>
+    </row>
+    <row r="253" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C253" t="s">
+        <v>401</v>
+      </c>
+      <c r="D253" s="6">
+        <v>1.445594606024259</v>
+      </c>
+    </row>
+    <row r="254" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C254" t="s">
+        <v>402</v>
+      </c>
+      <c r="D254" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C255" t="s">
+        <v>403</v>
+      </c>
+      <c r="D255" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+    </row>
+    <row r="256" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C256" t="s">
+        <v>404</v>
+      </c>
+      <c r="D256" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+    </row>
+    <row r="257" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C257" t="s">
+        <v>405</v>
+      </c>
+      <c r="D257" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+    </row>
+    <row r="258" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C258" t="s">
+        <v>406</v>
+      </c>
+      <c r="D258" s="6">
+        <v>1.3306500000000001</v>
+      </c>
+    </row>
+    <row r="259" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C259" t="s">
+        <v>407</v>
+      </c>
+      <c r="D259" s="6">
+        <v>1.168490303922999</v>
+      </c>
+    </row>
+    <row r="260" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C260" t="s">
+        <v>408</v>
+      </c>
+      <c r="D260" s="6">
+        <v>0.96197164445271299</v>
+      </c>
+    </row>
+    <row r="261" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C261" t="s">
+        <v>409</v>
+      </c>
+      <c r="D261" s="6">
+        <v>0.81485018268060216</v>
+      </c>
+    </row>
+    <row r="262" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C262" t="s">
+        <v>410</v>
+      </c>
+      <c r="D262" s="6">
+        <v>0.75817145378888506</v>
+      </c>
+    </row>
+    <row r="263" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C263" t="s">
+        <v>411</v>
+      </c>
+      <c r="D263" s="6">
+        <v>0.7629196125137071</v>
+      </c>
+    </row>
+    <row r="264" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C264" t="s">
+        <v>412</v>
+      </c>
+      <c r="D264" s="6">
+        <v>0.77932183257845977</v>
+      </c>
+    </row>
+    <row r="265" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C265" t="s">
+        <v>413</v>
+      </c>
+      <c r="D265" s="6">
+        <v>0.93070326310012352</v>
+      </c>
+    </row>
+    <row r="266" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C266" t="s">
+        <v>414</v>
+      </c>
+      <c r="D266" s="6">
+        <v>1.24417</v>
+      </c>
+    </row>
+    <row r="267" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C267" t="s">
+        <v>415</v>
+      </c>
+      <c r="D267" s="6">
+        <v>1.24417</v>
+      </c>
+    </row>
+    <row r="268" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C268" t="s">
+        <v>416</v>
+      </c>
+      <c r="D268" s="6">
+        <v>1.2139375122730589</v>
+      </c>
+    </row>
+    <row r="269" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C269" t="s">
+        <v>417</v>
+      </c>
+      <c r="D269" s="6">
+        <v>1.1335817884406301</v>
+      </c>
+    </row>
+    <row r="270" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C270" t="s">
+        <v>418</v>
+      </c>
+      <c r="D270" s="6">
+        <v>1.0212039989496859</v>
+      </c>
+    </row>
+    <row r="271" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C271" t="s">
+        <v>419</v>
+      </c>
+      <c r="D271" s="6">
+        <v>0.88244589954815522</v>
+      </c>
+    </row>
+    <row r="272" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C272" t="s">
+        <v>420</v>
+      </c>
+      <c r="D272" s="6">
+        <v>0.73269105197374251</v>
+      </c>
+    </row>
+    <row r="273" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C273" t="s">
+        <v>421</v>
+      </c>
+      <c r="D273" s="6">
+        <v>0.50911208970521893</v>
+      </c>
+    </row>
+    <row r="274" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C274" t="s">
+        <v>422</v>
+      </c>
+      <c r="D274" s="6">
+        <v>0.2239300037283849</v>
+      </c>
+    </row>
+    <row r="275" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C275" t="s">
+        <v>423</v>
+      </c>
+      <c r="D275" s="6">
+        <v>1.24417</v>
+      </c>
+    </row>
+    <row r="276" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C276" t="s">
+        <v>424</v>
+      </c>
+      <c r="D276" s="6">
+        <v>1.24417</v>
+      </c>
+    </row>
+    <row r="277" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C277" t="s">
+        <v>425</v>
+      </c>
+      <c r="D277" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C278" t="s">
+        <v>426</v>
+      </c>
+      <c r="D278" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C279" t="s">
+        <v>427</v>
+      </c>
+      <c r="D279" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C280" t="s">
+        <v>428</v>
+      </c>
+      <c r="D280" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C281" t="s">
+        <v>429</v>
+      </c>
+      <c r="D281" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C282" t="s">
+        <v>430</v>
+      </c>
+      <c r="D282" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C283" t="s">
+        <v>431</v>
+      </c>
+      <c r="D283" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C284" t="s">
+        <v>432</v>
+      </c>
+      <c r="D284" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C285" t="s">
+        <v>433</v>
+      </c>
+      <c r="D285" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C286" t="s">
+        <v>434</v>
+      </c>
+      <c r="D286" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C287" t="s">
+        <v>435</v>
+      </c>
+      <c r="D287" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C288" t="s">
+        <v>436</v>
+      </c>
+      <c r="D288" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C289" t="s">
+        <v>437</v>
+      </c>
+      <c r="D289" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C290" t="s">
+        <v>438</v>
+      </c>
+      <c r="D290" s="6">
+        <v>1.14602</v>
+      </c>
+    </row>
+    <row r="291" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C291" t="s">
+        <v>439</v>
+      </c>
+      <c r="D291" s="6">
+        <v>1.808411320529228</v>
+      </c>
+    </row>
+    <row r="292" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C292" t="s">
+        <v>440</v>
+      </c>
+      <c r="D292" s="6">
+        <v>2.1601397818328132</v>
+      </c>
+    </row>
+    <row r="293" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C293" t="s">
+        <v>441</v>
+      </c>
+      <c r="D293" s="6">
+        <v>2.24250419398009</v>
+      </c>
+    </row>
+    <row r="294" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C294" t="s">
+        <v>442</v>
+      </c>
+      <c r="D294" s="6">
+        <v>2.03692580601991</v>
+      </c>
+    </row>
+    <row r="295" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C295" t="s">
+        <v>443</v>
+      </c>
+      <c r="D295" s="6">
+        <v>2.041209752066115</v>
+      </c>
+    </row>
+    <row r="296" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C296" t="s">
+        <v>444</v>
+      </c>
+      <c r="D296" s="6">
+        <v>2.0828353719008259</v>
+      </c>
+    </row>
+    <row r="297" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C297" t="s">
+        <v>445</v>
+      </c>
+      <c r="D297" s="6">
+        <v>1.921141834722184</v>
+      </c>
+    </row>
+    <row r="298" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C298" t="s">
+        <v>446</v>
+      </c>
+      <c r="D298" s="6">
+        <v>1.811465933907441</v>
+      </c>
+    </row>
+    <row r="299" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C299" t="s">
+        <v>447</v>
+      </c>
+      <c r="D299" s="6">
+        <v>1.784668685038385</v>
+      </c>
+    </row>
+    <row r="300" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C300" t="s">
+        <v>448</v>
+      </c>
+      <c r="D300" s="6">
+        <v>1.7828779210370529</v>
+      </c>
+    </row>
+    <row r="301" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C301" t="s">
+        <v>449</v>
+      </c>
+      <c r="D301" s="6">
+        <v>1.7992483504831269</v>
+      </c>
+    </row>
+    <row r="302" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C302" t="s">
+        <v>450</v>
+      </c>
+      <c r="D302" s="6">
+        <v>1.9867300000000001</v>
+      </c>
+    </row>
+    <row r="303" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C303" t="s">
+        <v>451</v>
+      </c>
+      <c r="D303" s="6">
+        <v>1.949313383897203</v>
+      </c>
+    </row>
+    <row r="304" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C304" t="s">
+        <v>452</v>
+      </c>
+      <c r="D304" s="6">
+        <v>1.8922385595326849</v>
+      </c>
+    </row>
+    <row r="305" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C305" t="s">
+        <v>453</v>
+      </c>
+      <c r="D305" s="6">
+        <v>1.8036949520898209</v>
+      </c>
+    </row>
+    <row r="306" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C306" t="s">
+        <v>454</v>
+      </c>
+      <c r="D306" s="6">
+        <v>1.6994167692579401</v>
+      </c>
+    </row>
+    <row r="307" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C307" t="s">
+        <v>455</v>
+      </c>
+      <c r="D307" s="6">
+        <v>1.579696318604104</v>
+      </c>
+    </row>
+    <row r="308" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C308" t="s">
+        <v>456</v>
+      </c>
+      <c r="D308" s="6">
+        <v>1.4319443921254269</v>
+      </c>
+    </row>
+    <row r="309" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C309" t="s">
+        <v>457</v>
+      </c>
+      <c r="D309" s="6">
+        <v>1.241017216258639</v>
+      </c>
+    </row>
+    <row r="310" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C310" t="s">
+        <v>458</v>
+      </c>
+      <c r="D310" s="6">
+        <v>1.1492563783176311</v>
+      </c>
+    </row>
+    <row r="311" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C311" t="s">
+        <v>459</v>
+      </c>
+      <c r="D311" s="6">
+        <v>1.1275159230580361</v>
+      </c>
+    </row>
+    <row r="312" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C312" t="s">
+        <v>460</v>
+      </c>
+      <c r="D312" s="6">
+        <v>1.2752039899565639</v>
+      </c>
+    </row>
+    <row r="313" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C313" t="s">
+        <v>461</v>
+      </c>
+      <c r="D313" s="6">
+        <v>1.3216699999999999</v>
+      </c>
+    </row>
+    <row r="314" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C314" t="s">
+        <v>462</v>
+      </c>
+      <c r="D314" s="6">
+        <v>1.9253199999999999</v>
+      </c>
+    </row>
+    <row r="315" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C315" t="s">
+        <v>463</v>
+      </c>
+      <c r="D315" s="6">
+        <v>2.163478071508667</v>
+      </c>
+    </row>
+    <row r="316" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C316" t="s">
+        <v>464</v>
+      </c>
+      <c r="D316" s="6">
+        <v>2.514182641801479</v>
+      </c>
+    </row>
+    <row r="317" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C317" t="s">
+        <v>465</v>
+      </c>
+      <c r="D317" s="6">
+        <v>2.498727573881705</v>
+      </c>
+    </row>
+    <row r="318" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C318" t="s">
+        <v>466</v>
+      </c>
+      <c r="D318" s="6">
+        <v>2.4648542661039898</v>
+      </c>
+    </row>
+    <row r="319" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C319" t="s">
+        <v>467</v>
+      </c>
+      <c r="D319" s="6">
+        <v>2.4133352823849279</v>
+      </c>
+    </row>
+    <row r="320" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C320" t="s">
+        <v>468</v>
+      </c>
+      <c r="D320" s="6">
+        <v>2.2825934623166759</v>
+      </c>
+    </row>
+    <row r="321" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C321" t="s">
+        <v>469</v>
+      </c>
+      <c r="D321" s="6">
+        <v>2.074356410092979</v>
+      </c>
+    </row>
+    <row r="322" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C322" t="s">
+        <v>470</v>
+      </c>
+      <c r="D322" s="6">
+        <v>1.9822641849013141</v>
+      </c>
+    </row>
+    <row r="323" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C323" t="s">
+        <v>471</v>
+      </c>
+      <c r="D323" s="6">
+        <v>1.9253199999999999</v>
+      </c>
+    </row>
+    <row r="324" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C324" t="s">
+        <v>472</v>
+      </c>
+      <c r="D324" s="6">
+        <v>1.9253199999999999</v>
+      </c>
+    </row>
+    <row r="325" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C325" t="s">
+        <v>473</v>
+      </c>
+      <c r="D325" s="6">
+        <v>1.94462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -42235,13 +45049,10 @@
   <sheetPr>
     <tabColor rgb="FFCCFF33"/>
   </sheetPr>
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -42249,3438 +45060,1121 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1950.03</v>
       </c>
       <c r="B2" s="6">
         <v>0.51354299999999997</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.51354299999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1950.08</v>
       </c>
       <c r="B3" s="6">
         <v>0.72190900000000002</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.75704585995744056</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1950.11</v>
       </c>
       <c r="B4" s="6">
         <v>0.94341600000000003</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1.1093725198521249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1950.2</v>
       </c>
       <c r="B5" s="6">
         <v>1.2097100000000001</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1.3903823655241381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>1950.38</v>
       </c>
       <c r="B6" s="6">
         <v>1.8086599999999999</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1.7270944510541251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1950.59</v>
       </c>
       <c r="B7" s="6">
         <v>1.6778</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1.803151034958292</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>1950.74</v>
       </c>
       <c r="B8" s="6">
         <v>1.4623200000000001</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1.757510657656933</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>1950.89</v>
       </c>
       <c r="B9" s="6">
         <v>1.238</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1.68509628555894</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>1950.95</v>
       </c>
       <c r="B10" s="6">
         <v>1.0438499999999999</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.578987316219961</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>1951.05</v>
       </c>
       <c r="B11" s="6">
         <v>1.0711999999999999</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1.4504647878730541</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>1951.18</v>
       </c>
       <c r="B12" s="6">
         <v>1.4042600000000001</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.3358826592912481</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>1951.32</v>
       </c>
       <c r="B13" s="6">
         <v>1.3789199999999999</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1.1616573740675089</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>1951.67</v>
       </c>
       <c r="B14" s="6">
         <v>0.99704999999999999</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.0711999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>1951.82</v>
       </c>
       <c r="B15" s="6">
         <v>0.73732900000000001</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.206497777242679</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>1951.95</v>
       </c>
       <c r="B16" s="6">
         <v>0.83145599999999997</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.3965272467791621</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>1952.14</v>
       </c>
       <c r="B17" s="6">
         <v>2.16492</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.3967900795749091</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>1952.3</v>
       </c>
       <c r="B18" s="6">
         <v>2.1309999999999998</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.3753804141731509</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>1952.64</v>
       </c>
       <c r="B19" s="6">
         <v>1.7888200000000001</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.320815002718609</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>1952.8</v>
       </c>
       <c r="B20" s="6">
         <v>1.4495800000000001</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.232586018823786</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>1952.94</v>
       </c>
       <c r="B21" s="6">
         <v>1.49061</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.1199356043037509</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>1953.09</v>
       </c>
       <c r="B22" s="6">
         <v>1.89019</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.0008245962414051</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>1953.26</v>
       </c>
       <c r="B23" s="6">
         <v>1.9536100000000001</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.8321449458623581</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>1953.85</v>
       </c>
       <c r="B24" s="6">
         <v>1.28627</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.73787329440999982</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1954.17</v>
       </c>
       <c r="B25" s="6">
         <v>1.46608</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0.78223346986131936</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>1954.24</v>
       </c>
       <c r="B26" s="6">
         <v>1.3163</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="6">
-        <v>2.16492</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>1954.41</v>
       </c>
       <c r="B27" s="6">
         <v>1.25583</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D27" s="6">
-        <v>2.16492</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1954.79</v>
       </c>
       <c r="B28" s="6">
         <v>0.39635300000000001</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2.1637789529322369</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>1955.23</v>
       </c>
       <c r="B29" s="6">
         <v>1.87812</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" s="6">
-        <v>2.1464335909664731</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>1955.53</v>
       </c>
       <c r="B30" s="6">
         <v>1.68611</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="6">
-        <v>2.1173583135798162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>1955.64</v>
       </c>
       <c r="B31" s="6">
         <v>1.4702299999999999</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="6">
-        <v>2.0578582099449449</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>1955.8</v>
       </c>
       <c r="B32" s="6">
         <v>1.17082</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1.973092941523054</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>1955.92</v>
       </c>
       <c r="B33" s="6">
         <v>1.1630499999999999</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1.865380669716741</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>1956.03</v>
       </c>
       <c r="B34" s="6">
         <v>1.28345</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.7285274306977909</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>1956.18</v>
       </c>
       <c r="B35" s="6">
         <v>1.49718</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1.506120447323956</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>1956.2</v>
       </c>
       <c r="B36" s="6">
         <v>1.64334</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1.450380710628129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>1956.29</v>
       </c>
       <c r="B37" s="6">
         <v>1.6485700000000001</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1.4744370459717799</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>1956.52</v>
       </c>
       <c r="B38" s="6">
         <v>1.4558899999999999</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D38" s="6">
-        <v>1.89019</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>1956.8</v>
       </c>
       <c r="B39" s="6">
         <v>1.0557799999999999</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1.89019</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>1957.12</v>
       </c>
       <c r="B40" s="6">
         <v>1.8727499999999999</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1.9324895889503531</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>1957.29</v>
       </c>
       <c r="B41" s="6">
         <v>1.91405</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1.953320497661643</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>1957.68</v>
       </c>
       <c r="B42" s="6">
         <v>1.52373</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1.9442319873710121</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>1957.77</v>
       </c>
       <c r="B43" s="6">
         <v>1.24135</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1.9083090059560901</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>1957.88</v>
       </c>
       <c r="B44" s="6">
         <v>1.15822</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1.847560370035948</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>1958.11</v>
       </c>
       <c r="B45" s="6">
         <v>2.1735000000000002</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1.7575418836484611</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1958.5</v>
       </c>
       <c r="B46" s="6">
         <v>1.9115</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1.6394311130655239</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1958.52</v>
       </c>
       <c r="B47" s="6">
         <v>1.7788999999999999</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1.498001203077288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1958.67</v>
       </c>
       <c r="B48" s="6">
         <v>1.70059</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="6">
-        <v>1.323429206117086</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1958.7</v>
       </c>
       <c r="B49" s="6">
         <v>1.43537</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D49" s="6">
-        <v>1.28627</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1958.79</v>
       </c>
       <c r="B50" s="6">
         <v>1.4538800000000001</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50" s="6">
-        <v>1.46608</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1958.92</v>
       </c>
       <c r="B51" s="6">
         <v>1.36216</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1.46608</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1959.11</v>
       </c>
       <c r="B52" s="6">
         <v>1.8150999999999999</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1.46608</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1959.41</v>
       </c>
       <c r="B53" s="6">
         <v>1.5478700000000001</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1.3110264723159499</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1959.67</v>
       </c>
       <c r="B54" s="6">
         <v>1.14307</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1.2823204853596419</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1959.8</v>
       </c>
       <c r="B55" s="6">
         <v>0.91418600000000005</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1.2525836061255771</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1959.89</v>
       </c>
       <c r="B56" s="6">
         <v>0.95923800000000004</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1.166404096844694</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1959.94</v>
       </c>
       <c r="B57" s="6">
         <v>1.11893</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" s="6">
-        <v>1.009930285763476</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1960.11</v>
       </c>
       <c r="B58" s="6">
         <v>1.0496099999999999</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D58" s="6">
-        <v>0.79444843783937813</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1960.21</v>
       </c>
       <c r="B59" s="6">
         <v>1.1080700000000001</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D59" s="6">
-        <v>0.53879735552379526</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1960.33</v>
       </c>
       <c r="B60" s="6">
         <v>0</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1.46608</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1960.77</v>
       </c>
       <c r="B61" s="6">
         <v>0</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D61" s="6">
-        <v>0.39635300000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1960.82</v>
       </c>
       <c r="B62" s="6">
         <v>0.52051499999999995</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D62" s="6">
-        <v>1.87812</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1961.05</v>
       </c>
       <c r="B63" s="6">
         <v>1.42961</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D63" s="6">
-        <v>1.87812</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1961.48</v>
       </c>
       <c r="B64" s="6">
         <v>0.87154699999999996</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D64" s="6">
-        <v>1.87812</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1961.68</v>
       </c>
       <c r="B65" s="6">
         <v>1.1874499999999999</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D65" s="6">
-        <v>1.8770816314984149</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A66" s="7">
         <v>1961.86</v>
       </c>
       <c r="B66" s="8">
         <v>0.97666900000000001</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D66" s="6">
-        <v>1.851231577241552</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1961.97</v>
       </c>
       <c r="B67" s="6">
         <v>1.0041599999999999</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1.7947077788486581</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1962.14</v>
       </c>
       <c r="B68" s="6">
         <v>1.5233300000000001</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D68" s="6">
-        <v>1.719762490170663</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1962.27</v>
       </c>
       <c r="B69" s="6">
         <v>1.5289600000000001</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D69" s="6">
-        <v>1.5962880582532151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1962.38</v>
       </c>
       <c r="B70" s="6">
         <v>1.55202</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D70" s="6">
-        <v>1.410873716196873</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1962.55</v>
       </c>
       <c r="B71" s="6">
         <v>1.1906699999999999</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D71" s="6">
-        <v>1.2218791727083911</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1962.83</v>
       </c>
       <c r="B72" s="6">
         <v>0.94542800000000005</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D72" s="6">
-        <v>1.167072585532491</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1963.15</v>
       </c>
       <c r="B73" s="6">
         <v>1.7535499999999999</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D73" s="6">
-        <v>1.1630545836867161</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1963.24</v>
       </c>
       <c r="B74" s="6">
         <v>1.78976</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" s="6">
-        <v>1.28345</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1963.71</v>
       </c>
       <c r="B75" s="6">
         <v>1.1390499999999999</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D75" s="6">
-        <v>1.315249417840854</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1963.83</v>
       </c>
       <c r="B76" s="6">
         <v>1.09145</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D76" s="6">
-        <v>1.4606205467224309</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1963.86</v>
       </c>
       <c r="B77" s="6">
         <v>1.6359600000000001</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D77" s="6">
-        <v>1.647831852371733</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1964.05</v>
       </c>
       <c r="B78" s="6">
         <v>1.8012900000000001</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D78" s="6">
-        <v>1.637343179120254</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1964.76</v>
       </c>
       <c r="B79" s="6">
         <v>1.0907800000000001</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D79" s="6">
-        <v>1.56835889059592</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1964.95</v>
       </c>
       <c r="B80" s="6">
         <v>1.3712800000000001</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D80" s="6">
-        <v>1.4765656980012449</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1965.15</v>
       </c>
       <c r="B81" s="6">
         <v>1.47479</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D81" s="6">
-        <v>1.3803692210650369</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1965.42</v>
       </c>
       <c r="B82" s="6">
         <v>1.36216</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D82" s="6">
-        <v>1.2646366668457829</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1965.64</v>
       </c>
       <c r="B83" s="6">
         <v>1.06758</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D83" s="6">
-        <v>1.135494185445159</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1965.74</v>
       </c>
       <c r="B84" s="6">
         <v>0.68356099999999997</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D84" s="6">
-        <v>1.28345</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1965.98</v>
       </c>
       <c r="B85" s="6">
         <v>0.85827299999999995</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="D85" s="6">
-        <v>1.0557799999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1966.05</v>
       </c>
       <c r="B86" s="6">
         <v>1.02695</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D86" s="6">
-        <v>1.8727499999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1966.14</v>
       </c>
       <c r="B87" s="6">
         <v>1.0896999999999999</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D87" s="6">
-        <v>1.8727499999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1966.44</v>
       </c>
       <c r="B88" s="6">
         <v>0.747251</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D88" s="6">
-        <v>1.8944937991630051</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1966.59</v>
       </c>
       <c r="B89" s="6">
         <v>0.32823799999999997</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D89" s="6">
-        <v>1.9126252951405309</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1966.71</v>
       </c>
       <c r="B90" s="6">
         <v>0.271789</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D90" s="6">
-        <v>1.9085985522233651</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1966.85</v>
       </c>
       <c r="B91" s="6">
         <v>0.45883600000000002</v>
       </c>
-      <c r="C91" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D91" s="6">
-        <v>1.865416851639019</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1966.94</v>
       </c>
       <c r="B92" s="6">
         <v>0.42424200000000001</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D92" s="6">
-        <v>1.788256993805184</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1967.17</v>
       </c>
       <c r="B93" s="6">
         <v>0.908555</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D93" s="6">
-        <v>1.678962642685103</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1967.29</v>
       </c>
       <c r="B94" s="6">
         <v>0.94060100000000002</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D94" s="6">
-        <v>1.5467233686231141</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1967.61</v>
       </c>
       <c r="B95" s="6">
         <v>0.48766399999999999</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D95" s="6">
-        <v>1.291935619326027</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>1967.62</v>
       </c>
       <c r="B96" s="6">
         <v>0</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D96" s="6">
-        <v>1.1763337701770991</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1967.89</v>
       </c>
       <c r="B97" s="6">
         <v>0</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D97" s="6">
-        <v>1.15822</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>1967.89</v>
       </c>
       <c r="B98" s="6">
         <v>0.2203</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D98" s="6">
-        <v>2.1735000000000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>1968.06</v>
       </c>
       <c r="B99" s="6">
         <v>0.243899</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D99" s="6">
-        <v>2.1735000000000002</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1968.12</v>
       </c>
       <c r="B100" s="6">
         <v>0</v>
       </c>
-      <c r="C100" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D100" s="6">
-        <v>2.1705353937924539</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>1968.73</v>
       </c>
       <c r="B101" s="6">
         <v>0</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D101" s="6">
-        <v>2.1499569110631498</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>1968.89</v>
       </c>
       <c r="B102" s="6">
         <v>1.1317999999999999</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D102" s="6">
-        <v>2.1057662806240951</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>1969.08</v>
       </c>
       <c r="B103" s="6">
         <v>1.29271</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D103" s="6">
-        <v>2.028254832009301</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>1969.5</v>
       </c>
       <c r="B104" s="6">
         <v>0.92477900000000002</v>
       </c>
-      <c r="C104" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D104" s="6">
-        <v>1.915949960349512</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>1969.61</v>
       </c>
       <c r="B105" s="6">
         <v>0.56730999999999998</v>
       </c>
-      <c r="C105" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D105" s="6">
-        <v>1.7415139284031029</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>1969.77</v>
       </c>
       <c r="B106" s="6">
         <v>0.55993599999999999</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D106" s="6">
-        <v>1.703835572094538</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>1969.88</v>
       </c>
       <c r="B107" s="6">
         <v>1.3307899999999999</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D107" s="6">
-        <v>1.445883568745304</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>1969.97</v>
       </c>
       <c r="B108" s="6">
         <v>1.4068099999999999</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="D108" s="6">
-        <v>1.4415425020239869</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>1970.35</v>
       </c>
       <c r="B109" s="6">
         <v>0.91458799999999996</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D109" s="6">
-        <v>1.3655660193060219</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>1970.52</v>
       </c>
       <c r="B110" s="6">
         <v>0.83199199999999995</v>
       </c>
-      <c r="C110" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D110" s="6">
-        <v>1.8150999999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>1970.61</v>
       </c>
       <c r="B111" s="6">
         <v>0.50536300000000001</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D111" s="6">
-        <v>1.8150999999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>1970.76</v>
       </c>
       <c r="B112" s="6">
         <v>0.78988999999999998</v>
       </c>
-      <c r="C112" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D112" s="6">
-        <v>1.7829018207279781</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>1970.97</v>
       </c>
       <c r="B113" s="6">
         <v>1.7696400000000001</v>
       </c>
-      <c r="C113" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D113" s="6">
-        <v>1.7151242559679909</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>1971.36</v>
       </c>
       <c r="B114" s="6">
         <v>1.3306500000000001</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D114" s="6">
-        <v>1.6350676697888871</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>1971.67</v>
       </c>
       <c r="B115" s="6">
         <v>0.75811200000000001</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D115" s="6">
-        <v>1.5415254307848789</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A116" s="7">
         <v>1971.86</v>
       </c>
       <c r="B116" s="8">
         <v>0.78640399999999999</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="D116" s="6">
-        <v>1.429684970103092</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>1971.98</v>
       </c>
       <c r="B117" s="6">
         <v>1.2476499999999999</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="D117" s="6">
-        <v>1.291978210910204</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>1972.09</v>
       </c>
       <c r="B118" s="6">
         <v>1.24417</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D118" s="6">
-        <v>1.1476546625095849</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>1972.47</v>
       </c>
       <c r="B119" s="6">
         <v>0.791767</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D119" s="6">
-        <v>0.96970587619619142</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>1972.73</v>
       </c>
       <c r="B120" s="6">
         <v>0</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D120" s="6">
-        <v>0.9218577221459282</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>1973.76</v>
       </c>
       <c r="B121" s="6">
         <v>0</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D121" s="6">
-        <v>1.0236500140800091</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>1974</v>
       </c>
       <c r="B122" s="9">
         <v>1.14602</v>
       </c>
-      <c r="C122" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="D122" s="6">
-        <v>1.0496099999999999</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>1974.23</v>
       </c>
       <c r="B123" s="9">
         <v>2.2586499999999998</v>
       </c>
-      <c r="C123" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="D123" s="6">
-        <v>1.0496099999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>1974.35</v>
       </c>
       <c r="B124" s="9">
         <v>2.0207799999999998</v>
       </c>
-      <c r="C124" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="D124" s="6">
-        <v>1.102937709190672</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>1974.53</v>
       </c>
       <c r="B125" s="9">
         <v>2.0887600000000002</v>
       </c>
-      <c r="C125" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="D125" s="6">
-        <v>0.80953733541510142</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>1974.61</v>
       </c>
       <c r="B126" s="9">
         <v>1.8460700000000001</v>
       </c>
-      <c r="C126" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D126" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>1974.79</v>
       </c>
       <c r="B127" s="9">
         <v>1.7813099999999999</v>
       </c>
-      <c r="C127" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D127" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>1974.92</v>
       </c>
       <c r="B128" s="9">
         <v>1.8002100000000001</v>
       </c>
-      <c r="C128" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="D128" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>1975</v>
       </c>
       <c r="B129" s="6">
         <v>1.9867300000000001</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D129" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>1975.09</v>
       </c>
       <c r="B130" s="6">
         <v>1.9477100000000001</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D130" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>1975.44</v>
       </c>
       <c r="B131" s="6">
         <v>1.5437099999999999</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D131" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>1975.64</v>
       </c>
       <c r="B132" s="6">
         <v>1.16492</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D132" s="6">
-        <v>1.0496099999999999</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>1975.74</v>
       </c>
       <c r="B133" s="6">
         <v>1.1260399999999999</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D133" s="6">
-        <v>0.52051499999999995</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>1975.85</v>
       </c>
       <c r="B134" s="6">
         <v>1.3216699999999999</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D134" s="6">
-        <v>1.42961</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>1976.06</v>
       </c>
       <c r="B135" s="6">
         <v>1.9253199999999999</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D135" s="6">
-        <v>1.3210510828718229</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>1976.15</v>
       </c>
       <c r="B136" s="6">
         <v>2.5146199999999999</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D136" s="6">
-        <v>1.1353316420513031</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>1976.44</v>
       </c>
       <c r="B137" s="6">
         <v>2.3976899999999999</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D137" s="6">
-        <v>0.99659229316564057</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>1976.59</v>
       </c>
       <c r="B138" s="6">
         <v>2.06718</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D138" s="6">
-        <v>0.91717969565583624</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>1976.74</v>
       </c>
       <c r="B139" s="6">
         <v>1.94462</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D139" s="6">
-        <v>0.87891346380898094</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C140" t="s">
-        <v>288</v>
-      </c>
-      <c r="D140" s="6">
-        <v>0.87759843003005011</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C141" t="s">
-        <v>289</v>
-      </c>
-      <c r="D141" s="6">
-        <v>1.0327438757535019</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C142" t="s">
-        <v>290</v>
-      </c>
-      <c r="D142" s="6">
-        <v>1.1832070153103851</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C143" t="s">
-        <v>291</v>
-      </c>
-      <c r="D143" s="6">
-        <v>1.117893229403732</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C144" t="s">
-        <v>292</v>
-      </c>
-      <c r="D144" s="6">
-        <v>0.98767297704870272</v>
-      </c>
-    </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C145" t="s">
-        <v>293</v>
-      </c>
-      <c r="D145" s="6">
-        <v>0.9803629996662846</v>
-      </c>
-    </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C146" t="s">
-        <v>294</v>
-      </c>
-      <c r="D146" s="6">
-        <v>1.5233300000000001</v>
-      </c>
-    </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C147" t="s">
-        <v>295</v>
-      </c>
-      <c r="D147" s="6">
-        <v>1.5233300000000001</v>
-      </c>
-    </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C148" t="s">
-        <v>296</v>
-      </c>
-      <c r="D148" s="6">
-        <v>1.5235356716207229</v>
-      </c>
-    </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C149" t="s">
-        <v>297</v>
-      </c>
-      <c r="D149" s="6">
-        <v>1.527413984596925</v>
-      </c>
-    </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C150" t="s">
-        <v>298</v>
-      </c>
-      <c r="D150" s="6">
-        <v>1.543113247445089</v>
-      </c>
-    </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C151" t="s">
-        <v>299</v>
-      </c>
-      <c r="D151" s="6">
-        <v>1.5186126757841321</v>
-      </c>
-    </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C152" t="s">
-        <v>300</v>
-      </c>
-      <c r="D152" s="6">
-        <v>1.3038780764313</v>
-      </c>
-    </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C153" t="s">
-        <v>301</v>
-      </c>
-      <c r="D153" s="6">
-        <v>1.148710173631996</v>
-      </c>
-    </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C154" t="s">
-        <v>302</v>
-      </c>
-      <c r="D154" s="6">
-        <v>1.048854462359752</v>
-      </c>
-    </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C155" t="s">
-        <v>303</v>
-      </c>
-      <c r="D155" s="6">
-        <v>0.97691852043211502</v>
-      </c>
-    </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C156" t="s">
-        <v>304</v>
-      </c>
-      <c r="D156" s="6">
-        <v>1.5233300000000001</v>
-      </c>
-    </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C157" t="s">
-        <v>305</v>
-      </c>
-      <c r="D157" s="6">
-        <v>0.94542800000000005</v>
-      </c>
-    </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C158" t="s">
-        <v>306</v>
-      </c>
-      <c r="D158" s="6">
-        <v>1.7535499999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C159" t="s">
-        <v>307</v>
-      </c>
-      <c r="D159" s="6">
-        <v>1.7535499999999999</v>
-      </c>
-    </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C160" t="s">
-        <v>308</v>
-      </c>
-      <c r="D160" s="6">
-        <v>1.7625696848194869</v>
-      </c>
-    </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C161" t="s">
-        <v>309</v>
-      </c>
-      <c r="D161" s="6">
-        <v>1.7892524033254851</v>
-      </c>
-    </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C162" t="s">
-        <v>310</v>
-      </c>
-      <c r="D162" s="6">
-        <v>1.7349916208671179</v>
-      </c>
-    </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C163" t="s">
-        <v>311</v>
-      </c>
-      <c r="D163" s="6">
-        <v>1.609611726351591</v>
-      </c>
-    </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C164" t="s">
-        <v>312</v>
-      </c>
-      <c r="D164" s="6">
-        <v>1.455103208410264</v>
-      </c>
-    </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C165" t="s">
-        <v>313</v>
-      </c>
-      <c r="D165" s="6">
-        <v>1.2965819728015451</v>
-      </c>
-    </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C166" t="s">
-        <v>314</v>
-      </c>
-      <c r="D166" s="6">
-        <v>1.175214023633472</v>
-      </c>
-    </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C167" t="s">
-        <v>315</v>
-      </c>
-      <c r="D167" s="6">
-        <v>1.117367713171034</v>
-      </c>
-    </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C168" t="s">
-        <v>316</v>
-      </c>
-      <c r="D168" s="6">
-        <v>1.1211107291830471</v>
-      </c>
-    </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C169" t="s">
-        <v>317</v>
-      </c>
-      <c r="D169" s="6">
-        <v>1.6359600000000001</v>
-      </c>
-    </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C170" t="s">
-        <v>318</v>
-      </c>
-      <c r="D170" s="6">
-        <v>1.8012900000000001</v>
-      </c>
-    </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C171" t="s">
-        <v>319</v>
-      </c>
-      <c r="D171" s="6">
-        <v>1.7008762554486869</v>
-      </c>
-    </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C172" t="s">
-        <v>320</v>
-      </c>
-      <c r="D172" s="6">
-        <v>1.5119117163656539</v>
-      </c>
-    </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C173" t="s">
-        <v>321</v>
-      </c>
-      <c r="D173" s="6">
-        <v>1.3580880126384649</v>
-      </c>
-    </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C174" t="s">
-        <v>322</v>
-      </c>
-      <c r="D174" s="6">
-        <v>1.2501577491795499</v>
-      </c>
-    </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C175" t="s">
-        <v>323</v>
-      </c>
-      <c r="D175" s="6">
-        <v>1.1740971419701129</v>
-      </c>
-    </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C176" t="s">
-        <v>324</v>
-      </c>
-      <c r="D176" s="6">
-        <v>1.1282769937116759</v>
-      </c>
-    </row>
-    <row r="177" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C177" t="s">
-        <v>325</v>
-      </c>
-      <c r="D177" s="6">
-        <v>1.102814194732141</v>
-      </c>
-    </row>
-    <row r="178" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C178" t="s">
-        <v>326</v>
-      </c>
-      <c r="D178" s="6">
-        <v>1.0926544740284141</v>
-      </c>
-    </row>
-    <row r="179" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C179" t="s">
-        <v>327</v>
-      </c>
-      <c r="D179" s="6">
-        <v>1.0907848939710449</v>
-      </c>
-    </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C180" t="s">
-        <v>328</v>
-      </c>
-      <c r="D180" s="6">
-        <v>1.1547466616118871</v>
-      </c>
-    </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C181" t="s">
-        <v>329</v>
-      </c>
-      <c r="D181" s="6">
-        <v>1.30943813322477</v>
-      </c>
-    </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C182" t="s">
-        <v>330</v>
-      </c>
-      <c r="D182" s="6">
-        <v>1.47479</v>
-      </c>
-    </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C183" t="s">
-        <v>331</v>
-      </c>
-      <c r="D183" s="6">
-        <v>1.47479</v>
-      </c>
-    </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C184" t="s">
-        <v>332</v>
-      </c>
-      <c r="D184" s="6">
-        <v>1.474381868335678</v>
-      </c>
-    </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C185" t="s">
-        <v>333</v>
-      </c>
-      <c r="D185" s="6">
-        <v>1.455698348058541</v>
-      </c>
-    </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C186" t="s">
-        <v>334</v>
-      </c>
-      <c r="D186" s="6">
-        <v>1.417340544002536</v>
-      </c>
-    </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C187" t="s">
-        <v>335</v>
-      </c>
-      <c r="D187" s="6">
-        <v>1.3656970983429011</v>
-      </c>
-    </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C188" t="s">
-        <v>336</v>
-      </c>
-      <c r="D188" s="6">
-        <v>1.294979023666085</v>
-      </c>
-    </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C189" t="s">
-        <v>337</v>
-      </c>
-      <c r="D189" s="6">
-        <v>1.1765534151952419</v>
-      </c>
-    </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C190" t="s">
-        <v>338</v>
-      </c>
-      <c r="D190" s="6">
-        <v>0.96784943659467682</v>
-      </c>
-    </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C191" t="s">
-        <v>339</v>
-      </c>
-      <c r="D191" s="6">
-        <v>0.6835681635573414</v>
-      </c>
-    </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C192" t="s">
-        <v>340</v>
-      </c>
-      <c r="D192" s="6">
-        <v>0.69398901695360538</v>
-      </c>
-    </row>
-    <row r="193" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C193" t="s">
-        <v>341</v>
-      </c>
-      <c r="D193" s="6">
-        <v>0.75311224354482809</v>
-      </c>
-    </row>
-    <row r="194" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C194" t="s">
-        <v>342</v>
-      </c>
-      <c r="D194" s="6">
-        <v>1.02695</v>
-      </c>
-    </row>
-    <row r="195" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C195" t="s">
-        <v>343</v>
-      </c>
-      <c r="D195" s="6">
-        <v>1.0631679881857969</v>
-      </c>
-    </row>
-    <row r="196" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C196" t="s">
-        <v>344</v>
-      </c>
-      <c r="D196" s="6">
-        <v>1.086972968940549</v>
-      </c>
-    </row>
-    <row r="197" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C197" t="s">
-        <v>345</v>
-      </c>
-      <c r="D197" s="6">
-        <v>1.0313265667786959</v>
-      </c>
-    </row>
-    <row r="198" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C198" t="s">
-        <v>346</v>
-      </c>
-      <c r="D198" s="6">
-        <v>0.9264772468142628</v>
-      </c>
-    </row>
-    <row r="199" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C199" t="s">
-        <v>347</v>
-      </c>
-      <c r="D199" s="6">
-        <v>0.78918242720145293</v>
-      </c>
-    </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C200" t="s">
-        <v>348</v>
-      </c>
-      <c r="D200" s="6">
-        <v>0.58383567670628755</v>
-      </c>
-    </row>
-    <row r="201" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C201" t="s">
-        <v>349</v>
-      </c>
-      <c r="D201" s="6">
-        <v>0.33685853191330511</v>
-      </c>
-    </row>
-    <row r="202" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C202" t="s">
-        <v>350</v>
-      </c>
-      <c r="D202" s="6">
-        <v>0.2808313839120441</v>
-      </c>
-    </row>
-    <row r="203" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C203" t="s">
-        <v>351</v>
-      </c>
-      <c r="D203" s="6">
-        <v>0.30633567887916408</v>
-      </c>
-    </row>
-    <row r="204" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C204" t="s">
-        <v>352</v>
-      </c>
-      <c r="D204" s="6">
-        <v>0.45167849216364753</v>
-      </c>
-    </row>
-    <row r="205" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C205" t="s">
-        <v>353</v>
-      </c>
-      <c r="D205" s="6">
-        <v>0.44436740725681712</v>
-      </c>
-    </row>
-    <row r="206" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C206" t="s">
-        <v>354</v>
-      </c>
-      <c r="D206" s="6">
-        <v>0.908555</v>
-      </c>
-    </row>
-    <row r="207" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C207" t="s">
-        <v>355</v>
-      </c>
-      <c r="D207" s="6">
-        <v>0.908555</v>
-      </c>
-    </row>
-    <row r="208" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C208" t="s">
-        <v>356</v>
-      </c>
-      <c r="D208" s="6">
-        <v>0.908555</v>
-      </c>
-    </row>
-    <row r="209" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C209" t="s">
-        <v>357</v>
-      </c>
-      <c r="D209" s="6">
-        <v>0.93838946437626203</v>
-      </c>
-    </row>
-    <row r="210" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C210" t="s">
-        <v>358</v>
-      </c>
-      <c r="D210" s="6">
-        <v>0.93794893868304563</v>
-      </c>
-    </row>
-    <row r="211" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C211" t="s">
-        <v>359</v>
-      </c>
-      <c r="D211" s="6">
-        <v>0.90196138384661972</v>
-      </c>
-    </row>
-    <row r="212" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C212" t="s">
-        <v>360</v>
-      </c>
-      <c r="D212" s="6">
-        <v>0.7989410966952607</v>
-      </c>
-    </row>
-    <row r="213" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C213" t="s">
-        <v>361</v>
-      </c>
-      <c r="D213" s="6">
-        <v>0.58568937882797245</v>
-      </c>
-    </row>
-    <row r="214" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C214" t="s">
-        <v>362</v>
-      </c>
-      <c r="D214" s="6">
-        <v>5.7498039719844623E-4</v>
-      </c>
-    </row>
-    <row r="215" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C215" t="s">
-        <v>363</v>
-      </c>
-      <c r="D215" s="6">
-        <v>1.215065942974441E-2</v>
-      </c>
-    </row>
-    <row r="216" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C216" t="s">
-        <v>364</v>
-      </c>
-      <c r="D216" s="6">
-        <v>5.5537980348324259E-2</v>
-      </c>
-    </row>
-    <row r="217" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C217" t="s">
-        <v>365</v>
-      </c>
-      <c r="D217" s="6">
-        <v>0.11015</v>
-      </c>
-    </row>
-    <row r="218" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C218" t="s">
-        <v>366</v>
-      </c>
-      <c r="D218" s="6">
-        <v>0.243899</v>
-      </c>
-    </row>
-    <row r="219" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C219" t="s">
-        <v>367</v>
-      </c>
-      <c r="D219" s="6">
-        <v>0.1025872424906852</v>
-      </c>
-    </row>
-    <row r="220" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C220" t="s">
-        <v>368</v>
-      </c>
-      <c r="D220" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C221" t="s">
-        <v>369</v>
-      </c>
-      <c r="D221" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C222" t="s">
-        <v>370</v>
-      </c>
-      <c r="D222" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C223" t="s">
-        <v>371</v>
-      </c>
-      <c r="D223" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C224" t="s">
-        <v>372</v>
-      </c>
-      <c r="D224" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C225" t="s">
-        <v>373</v>
-      </c>
-      <c r="D225" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C226" t="s">
-        <v>374</v>
-      </c>
-      <c r="D226" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C227" t="s">
-        <v>375</v>
-      </c>
-      <c r="D227" s="6">
-        <v>3.6263529223620299E-2</v>
-      </c>
-    </row>
-    <row r="228" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C228" t="s">
-        <v>376</v>
-      </c>
-      <c r="D228" s="6">
-        <v>0.64476775512748663</v>
-      </c>
-    </row>
-    <row r="229" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C229" t="s">
-        <v>377</v>
-      </c>
-      <c r="D229" s="6">
-        <v>1.1317999999999999</v>
-      </c>
-    </row>
-    <row r="230" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C230" t="s">
-        <v>378</v>
-      </c>
-      <c r="D230" s="6">
-        <v>1.29271</v>
-      </c>
-    </row>
-    <row r="231" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C231" t="s">
-        <v>379</v>
-      </c>
-      <c r="D231" s="6">
-        <v>1.292633200311236</v>
-      </c>
-    </row>
-    <row r="232" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C232" t="s">
-        <v>380</v>
-      </c>
-      <c r="D232" s="6">
-        <v>1.2760112421702661</v>
-      </c>
-    </row>
-    <row r="233" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C233" t="s">
-        <v>381</v>
-      </c>
-      <c r="D233" s="6">
-        <v>1.226330182817519</v>
-      </c>
-    </row>
-    <row r="234" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C234" t="s">
-        <v>382</v>
-      </c>
-      <c r="D234" s="6">
-        <v>1.150712630816606</v>
-      </c>
-    </row>
-    <row r="235" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C235" t="s">
-        <v>383</v>
-      </c>
-      <c r="D235" s="6">
-        <v>1.0481296255543371</v>
-      </c>
-    </row>
-    <row r="236" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C236" t="s">
-        <v>384</v>
-      </c>
-      <c r="D236" s="6">
-        <v>0.92904000467391568</v>
-      </c>
-    </row>
-    <row r="237" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C237" t="s">
-        <v>385</v>
-      </c>
-      <c r="D237" s="6">
-        <v>0.61663751677134848</v>
-      </c>
-    </row>
-    <row r="238" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C238" t="s">
-        <v>386</v>
-      </c>
-      <c r="D238" s="6">
-        <v>0.56288248669627594</v>
-      </c>
-    </row>
-    <row r="239" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C239" t="s">
-        <v>387</v>
-      </c>
-      <c r="D239" s="6">
-        <v>0.56005947417004176</v>
-      </c>
-    </row>
-    <row r="240" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C240" t="s">
-        <v>388</v>
-      </c>
-      <c r="D240" s="6">
-        <v>1.008870092156436</v>
-      </c>
-    </row>
-    <row r="241" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C241" t="s">
-        <v>389</v>
-      </c>
-      <c r="D241" s="6">
-        <v>1.3760562711554309</v>
-      </c>
-    </row>
-    <row r="242" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C242" t="s">
-        <v>390</v>
-      </c>
-      <c r="D242" s="6">
-        <v>0.91458799999999996</v>
-      </c>
-    </row>
-    <row r="243" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C243" t="s">
-        <v>391</v>
-      </c>
-      <c r="D243" s="6">
-        <v>0.91458799999999996</v>
-      </c>
-    </row>
-    <row r="244" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C244" t="s">
-        <v>392</v>
-      </c>
-      <c r="D244" s="6">
-        <v>0.91458799999999996</v>
-      </c>
-    </row>
-    <row r="245" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C245" t="s">
-        <v>393</v>
-      </c>
-      <c r="D245" s="6">
-        <v>0.91458799999999996</v>
-      </c>
-    </row>
-    <row r="246" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C246" t="s">
-        <v>394</v>
-      </c>
-      <c r="D246" s="6">
-        <v>0.91458799999999996</v>
-      </c>
-    </row>
-    <row r="247" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C247" t="s">
-        <v>395</v>
-      </c>
-      <c r="D247" s="6">
-        <v>0.9015368868512933</v>
-      </c>
-    </row>
-    <row r="248" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C248" t="s">
-        <v>396</v>
-      </c>
-      <c r="D248" s="6">
-        <v>0.85121294196548991</v>
-      </c>
-    </row>
-    <row r="249" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C249" t="s">
-        <v>397</v>
-      </c>
-      <c r="D249" s="6">
-        <v>0.57178853299630461</v>
-      </c>
-    </row>
-    <row r="250" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C250" t="s">
-        <v>398</v>
-      </c>
-      <c r="D250" s="6">
-        <v>0.56250155066339425</v>
-      </c>
-    </row>
-    <row r="251" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C251" t="s">
-        <v>399</v>
-      </c>
-      <c r="D251" s="6">
-        <v>0.7608744435535848</v>
-      </c>
-    </row>
-    <row r="252" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C252" t="s">
-        <v>400</v>
-      </c>
-      <c r="D252" s="6">
-        <v>1.043326315604195</v>
-      </c>
-    </row>
-    <row r="253" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C253" t="s">
-        <v>401</v>
-      </c>
-      <c r="D253" s="6">
-        <v>1.445594606024259</v>
-      </c>
-    </row>
-    <row r="254" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C254" t="s">
-        <v>402</v>
-      </c>
-      <c r="D254" s="6">
-        <v>1.3306500000000001</v>
-      </c>
-    </row>
-    <row r="255" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C255" t="s">
-        <v>403</v>
-      </c>
-      <c r="D255" s="6">
-        <v>1.3306500000000001</v>
-      </c>
-    </row>
-    <row r="256" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C256" t="s">
-        <v>404</v>
-      </c>
-      <c r="D256" s="6">
-        <v>1.3306500000000001</v>
-      </c>
-    </row>
-    <row r="257" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C257" t="s">
-        <v>405</v>
-      </c>
-      <c r="D257" s="6">
-        <v>1.3306500000000001</v>
-      </c>
-    </row>
-    <row r="258" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C258" t="s">
-        <v>406</v>
-      </c>
-      <c r="D258" s="6">
-        <v>1.3306500000000001</v>
-      </c>
-    </row>
-    <row r="259" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C259" t="s">
-        <v>407</v>
-      </c>
-      <c r="D259" s="6">
-        <v>1.168490303922999</v>
-      </c>
-    </row>
-    <row r="260" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C260" t="s">
-        <v>408</v>
-      </c>
-      <c r="D260" s="6">
-        <v>0.96197164445271299</v>
-      </c>
-    </row>
-    <row r="261" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C261" t="s">
-        <v>409</v>
-      </c>
-      <c r="D261" s="6">
-        <v>0.81485018268060216</v>
-      </c>
-    </row>
-    <row r="262" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C262" t="s">
-        <v>410</v>
-      </c>
-      <c r="D262" s="6">
-        <v>0.75817145378888506</v>
-      </c>
-    </row>
-    <row r="263" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C263" t="s">
-        <v>411</v>
-      </c>
-      <c r="D263" s="6">
-        <v>0.7629196125137071</v>
-      </c>
-    </row>
-    <row r="264" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C264" t="s">
-        <v>412</v>
-      </c>
-      <c r="D264" s="6">
-        <v>0.77932183257845977</v>
-      </c>
-    </row>
-    <row r="265" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C265" t="s">
-        <v>413</v>
-      </c>
-      <c r="D265" s="6">
-        <v>0.93070326310012352</v>
-      </c>
-    </row>
-    <row r="266" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C266" t="s">
-        <v>414</v>
-      </c>
-      <c r="D266" s="6">
-        <v>1.24417</v>
-      </c>
-    </row>
-    <row r="267" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C267" t="s">
-        <v>415</v>
-      </c>
-      <c r="D267" s="6">
-        <v>1.24417</v>
-      </c>
-    </row>
-    <row r="268" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C268" t="s">
-        <v>416</v>
-      </c>
-      <c r="D268" s="6">
-        <v>1.2139375122730589</v>
-      </c>
-    </row>
-    <row r="269" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C269" t="s">
-        <v>417</v>
-      </c>
-      <c r="D269" s="6">
-        <v>1.1335817884406301</v>
-      </c>
-    </row>
-    <row r="270" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C270" t="s">
-        <v>418</v>
-      </c>
-      <c r="D270" s="6">
-        <v>1.0212039989496859</v>
-      </c>
-    </row>
-    <row r="271" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C271" t="s">
-        <v>419</v>
-      </c>
-      <c r="D271" s="6">
-        <v>0.88244589954815522</v>
-      </c>
-    </row>
-    <row r="272" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C272" t="s">
-        <v>420</v>
-      </c>
-      <c r="D272" s="6">
-        <v>0.73269105197374251</v>
-      </c>
-    </row>
-    <row r="273" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C273" t="s">
-        <v>421</v>
-      </c>
-      <c r="D273" s="6">
-        <v>0.50911208970521893</v>
-      </c>
-    </row>
-    <row r="274" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C274" t="s">
-        <v>422</v>
-      </c>
-      <c r="D274" s="6">
-        <v>0.2239300037283849</v>
-      </c>
-    </row>
-    <row r="275" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C275" t="s">
-        <v>423</v>
-      </c>
-      <c r="D275" s="6">
-        <v>1.24417</v>
-      </c>
-    </row>
-    <row r="276" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C276" t="s">
-        <v>424</v>
-      </c>
-      <c r="D276" s="6">
-        <v>1.24417</v>
-      </c>
-    </row>
-    <row r="277" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C277" t="s">
-        <v>425</v>
-      </c>
-      <c r="D277" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C278" t="s">
-        <v>426</v>
-      </c>
-      <c r="D278" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C279" t="s">
-        <v>427</v>
-      </c>
-      <c r="D279" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C280" t="s">
-        <v>428</v>
-      </c>
-      <c r="D280" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C281" t="s">
-        <v>429</v>
-      </c>
-      <c r="D281" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C282" t="s">
-        <v>430</v>
-      </c>
-      <c r="D282" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C283" t="s">
-        <v>431</v>
-      </c>
-      <c r="D283" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C284" t="s">
-        <v>432</v>
-      </c>
-      <c r="D284" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C285" t="s">
-        <v>433</v>
-      </c>
-      <c r="D285" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C286" t="s">
-        <v>434</v>
-      </c>
-      <c r="D286" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C287" t="s">
-        <v>435</v>
-      </c>
-      <c r="D287" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C288" t="s">
-        <v>436</v>
-      </c>
-      <c r="D288" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C289" t="s">
-        <v>437</v>
-      </c>
-      <c r="D289" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C290" t="s">
-        <v>438</v>
-      </c>
-      <c r="D290" s="6">
-        <v>1.14602</v>
-      </c>
-    </row>
-    <row r="291" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C291" t="s">
-        <v>439</v>
-      </c>
-      <c r="D291" s="6">
-        <v>1.808411320529228</v>
-      </c>
-    </row>
-    <row r="292" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C292" t="s">
-        <v>440</v>
-      </c>
-      <c r="D292" s="6">
-        <v>2.1601397818328132</v>
-      </c>
-    </row>
-    <row r="293" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C293" t="s">
-        <v>441</v>
-      </c>
-      <c r="D293" s="6">
-        <v>2.24250419398009</v>
-      </c>
-    </row>
-    <row r="294" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C294" t="s">
-        <v>442</v>
-      </c>
-      <c r="D294" s="6">
-        <v>2.03692580601991</v>
-      </c>
-    </row>
-    <row r="295" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C295" t="s">
-        <v>443</v>
-      </c>
-      <c r="D295" s="6">
-        <v>2.041209752066115</v>
-      </c>
-    </row>
-    <row r="296" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C296" t="s">
-        <v>444</v>
-      </c>
-      <c r="D296" s="6">
-        <v>2.0828353719008259</v>
-      </c>
-    </row>
-    <row r="297" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C297" t="s">
-        <v>445</v>
-      </c>
-      <c r="D297" s="6">
-        <v>1.921141834722184</v>
-      </c>
-    </row>
-    <row r="298" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C298" t="s">
-        <v>446</v>
-      </c>
-      <c r="D298" s="6">
-        <v>1.811465933907441</v>
-      </c>
-    </row>
-    <row r="299" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C299" t="s">
-        <v>447</v>
-      </c>
-      <c r="D299" s="6">
-        <v>1.784668685038385</v>
-      </c>
-    </row>
-    <row r="300" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C300" t="s">
-        <v>448</v>
-      </c>
-      <c r="D300" s="6">
-        <v>1.7828779210370529</v>
-      </c>
-    </row>
-    <row r="301" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C301" t="s">
-        <v>449</v>
-      </c>
-      <c r="D301" s="6">
-        <v>1.7992483504831269</v>
-      </c>
-    </row>
-    <row r="302" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C302" t="s">
-        <v>450</v>
-      </c>
-      <c r="D302" s="6">
-        <v>1.9867300000000001</v>
-      </c>
-    </row>
-    <row r="303" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C303" t="s">
-        <v>451</v>
-      </c>
-      <c r="D303" s="6">
-        <v>1.949313383897203</v>
-      </c>
-    </row>
-    <row r="304" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C304" t="s">
-        <v>452</v>
-      </c>
-      <c r="D304" s="6">
-        <v>1.8922385595326849</v>
-      </c>
-    </row>
-    <row r="305" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C305" t="s">
-        <v>453</v>
-      </c>
-      <c r="D305" s="6">
-        <v>1.8036949520898209</v>
-      </c>
-    </row>
-    <row r="306" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C306" t="s">
-        <v>454</v>
-      </c>
-      <c r="D306" s="6">
-        <v>1.6994167692579401</v>
-      </c>
-    </row>
-    <row r="307" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C307" t="s">
-        <v>455</v>
-      </c>
-      <c r="D307" s="6">
-        <v>1.579696318604104</v>
-      </c>
-    </row>
-    <row r="308" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C308" t="s">
-        <v>456</v>
-      </c>
-      <c r="D308" s="6">
-        <v>1.4319443921254269</v>
-      </c>
-    </row>
-    <row r="309" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C309" t="s">
-        <v>457</v>
-      </c>
-      <c r="D309" s="6">
-        <v>1.241017216258639</v>
-      </c>
-    </row>
-    <row r="310" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C310" t="s">
-        <v>458</v>
-      </c>
-      <c r="D310" s="6">
-        <v>1.1492563783176311</v>
-      </c>
-    </row>
-    <row r="311" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C311" t="s">
-        <v>459</v>
-      </c>
-      <c r="D311" s="6">
-        <v>1.1275159230580361</v>
-      </c>
-    </row>
-    <row r="312" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C312" t="s">
-        <v>460</v>
-      </c>
-      <c r="D312" s="6">
-        <v>1.2752039899565639</v>
-      </c>
-    </row>
-    <row r="313" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C313" t="s">
-        <v>461</v>
-      </c>
-      <c r="D313" s="6">
-        <v>1.3216699999999999</v>
-      </c>
-    </row>
-    <row r="314" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C314" t="s">
-        <v>462</v>
-      </c>
-      <c r="D314" s="6">
-        <v>1.9253199999999999</v>
-      </c>
-    </row>
-    <row r="315" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C315" t="s">
-        <v>463</v>
-      </c>
-      <c r="D315" s="6">
-        <v>2.163478071508667</v>
-      </c>
-    </row>
-    <row r="316" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C316" t="s">
-        <v>464</v>
-      </c>
-      <c r="D316" s="6">
-        <v>2.514182641801479</v>
-      </c>
-    </row>
-    <row r="317" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C317" t="s">
-        <v>465</v>
-      </c>
-      <c r="D317" s="6">
-        <v>2.498727573881705</v>
-      </c>
-    </row>
-    <row r="318" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C318" t="s">
-        <v>466</v>
-      </c>
-      <c r="D318" s="6">
-        <v>2.4648542661039898</v>
-      </c>
-    </row>
-    <row r="319" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C319" t="s">
-        <v>467</v>
-      </c>
-      <c r="D319" s="6">
-        <v>2.4133352823849279</v>
-      </c>
-    </row>
-    <row r="320" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C320" t="s">
-        <v>468</v>
-      </c>
-      <c r="D320" s="6">
-        <v>2.2825934623166759</v>
-      </c>
-    </row>
-    <row r="321" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C321" t="s">
-        <v>469</v>
-      </c>
-      <c r="D321" s="6">
-        <v>2.074356410092979</v>
-      </c>
-    </row>
-    <row r="322" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C322" t="s">
-        <v>470</v>
-      </c>
-      <c r="D322" s="6">
-        <v>1.9822641849013141</v>
-      </c>
-    </row>
-    <row r="323" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C323" t="s">
-        <v>471</v>
-      </c>
-      <c r="D323" s="6">
-        <v>1.9253199999999999</v>
-      </c>
-    </row>
-    <row r="324" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C324" t="s">
-        <v>472</v>
-      </c>
-      <c r="D324" s="6">
-        <v>1.9253199999999999</v>
-      </c>
-    </row>
-    <row r="325" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C325" t="s">
-        <v>473</v>
-      </c>
-      <c r="D325" s="6">
-        <v>1.94462</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08B4324-DAE2-4D42-87E0-ACF814584E93}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -45688,15 +46182,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="14">
         <v>1962</v>
       </c>
       <c r="B2" s="15">
         <v>576.15099999999995</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="14">
         <v>1963</v>
       </c>
@@ -45704,7 +46199,7 @@
         <v>3317.57</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="14">
         <v>1964</v>
       </c>
@@ -45712,7 +46207,7 @@
         <v>5418.26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="14">
         <v>1965</v>
       </c>
@@ -45720,7 +46215,7 @@
         <v>8891.94</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="14">
         <v>1966</v>
       </c>
@@ -45728,7 +46223,7 @@
         <v>7423.85</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="14">
         <v>1967</v>
       </c>
@@ -45736,7 +46231,7 @@
         <v>3299.77</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="14">
         <v>1968</v>
       </c>
@@ -45744,7 +46239,7 @@
         <v>91.533199999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="14">
         <v>1969</v>
       </c>
@@ -45752,7 +46247,7 @@
         <v>3473.18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="14">
         <v>1970</v>
       </c>
@@ -45760,7 +46255,7 @@
         <v>4291.8900000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="14">
         <v>1971</v>
       </c>
@@ -45768,7 +46263,7 @@
         <v>3464.02</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="14">
         <v>1972</v>
       </c>
@@ -45776,7 +46271,7 @@
         <v>5198.58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="14">
         <v>1973</v>
       </c>
@@ -45784,7 +46279,7 @@
         <v>2082.38</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="14">
         <v>1974</v>
       </c>
@@ -45792,7 +46287,7 @@
         <v>3176.2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="14">
         <v>1975</v>
       </c>
@@ -45800,7 +46295,7 @@
         <v>2438.34</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="14">
         <v>1976</v>
       </c>
